--- a/data/anexo_ena_2019_variedades_pastos.xlsx
+++ b/data/anexo_ena_2019_variedades_pastos.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bella\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bella\OneDrive\Documentos\Uni\Ing-Software-II-ForraTech-Proyect\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7F755B-FC21-4680-9BE0-BF997C400DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -2159,6 +2159,75 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="24" fillId="4" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="24" fillId="4" borderId="6" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="4" borderId="9" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="4" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="24" fillId="4" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="4" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2204,6 +2273,99 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
@@ -2213,170 +2375,8 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="24" fillId="4" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="24" fillId="4" borderId="6" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="4" borderId="9" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="4" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="24" fillId="4" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="4" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -3874,13 +3874,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
+      <c r="A1" s="129"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="12"/>
@@ -3891,62 +3891,62 @@
       <c r="G2" s="12"/>
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="107" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="108"/>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="109"/>
+      <c r="A3" s="130" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="131"/>
+      <c r="C3" s="131"/>
+      <c r="D3" s="131"/>
+      <c r="E3" s="131"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="132"/>
     </row>
     <row r="4" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="110"/>
-      <c r="B4" s="111"/>
-      <c r="C4" s="111"/>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="112"/>
+      <c r="A4" s="133"/>
+      <c r="B4" s="134"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="134"/>
+      <c r="E4" s="134"/>
+      <c r="F4" s="134"/>
+      <c r="G4" s="135"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="113" t="s">
+      <c r="A5" s="136" t="s">
         <v>160</v>
       </c>
-      <c r="B5" s="114"/>
-      <c r="C5" s="114"/>
-      <c r="D5" s="114"/>
-      <c r="E5" s="114"/>
-      <c r="F5" s="114"/>
-      <c r="G5" s="115"/>
+      <c r="B5" s="137"/>
+      <c r="C5" s="137"/>
+      <c r="D5" s="137"/>
+      <c r="E5" s="137"/>
+      <c r="F5" s="137"/>
+      <c r="G5" s="138"/>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="113"/>
-      <c r="B6" s="114"/>
-      <c r="C6" s="114"/>
-      <c r="D6" s="114"/>
-      <c r="E6" s="114"/>
-      <c r="F6" s="114"/>
-      <c r="G6" s="115"/>
+      <c r="A6" s="136"/>
+      <c r="B6" s="137"/>
+      <c r="C6" s="137"/>
+      <c r="D6" s="137"/>
+      <c r="E6" s="137"/>
+      <c r="F6" s="137"/>
+      <c r="G6" s="138"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="116"/>
-      <c r="B7" s="117"/>
-      <c r="C7" s="117"/>
-      <c r="D7" s="117"/>
-      <c r="E7" s="117"/>
-      <c r="F7" s="117"/>
-      <c r="G7" s="118"/>
+      <c r="A7" s="139"/>
+      <c r="B7" s="140"/>
+      <c r="C7" s="140"/>
+      <c r="D7" s="140"/>
+      <c r="E7" s="140"/>
+      <c r="F7" s="140"/>
+      <c r="G7" s="141"/>
     </row>
     <row r="8" spans="1:7" s="3" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="119" t="s">
+      <c r="B8" s="142" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="119"/>
+      <c r="C8" s="142"/>
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -3962,10 +3962,10 @@
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="120" t="s">
+      <c r="B10" s="143" t="s">
         <v>161</v>
       </c>
-      <c r="C10" s="120"/>
+      <c r="C10" s="143"/>
       <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -4468,38 +4468,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="146"/>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
-      <c r="H1" s="146"/>
-      <c r="I1" s="146"/>
-      <c r="J1" s="146"/>
-      <c r="K1" s="146"/>
-      <c r="L1" s="146"/>
-      <c r="M1" s="146"/>
-      <c r="N1" s="147" t="s">
+      <c r="A1" s="153"/>
+      <c r="B1" s="153"/>
+      <c r="C1" s="153"/>
+      <c r="D1" s="153"/>
+      <c r="E1" s="153"/>
+      <c r="F1" s="153"/>
+      <c r="G1" s="153"/>
+      <c r="H1" s="153"/>
+      <c r="I1" s="153"/>
+      <c r="J1" s="153"/>
+      <c r="K1" s="153"/>
+      <c r="L1" s="153"/>
+      <c r="M1" s="153"/>
+      <c r="N1" s="106" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="146"/>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="146"/>
-      <c r="G2" s="146"/>
-      <c r="H2" s="146"/>
-      <c r="I2" s="146"/>
-      <c r="J2" s="146"/>
-      <c r="K2" s="146"/>
-      <c r="L2" s="146"/>
-      <c r="M2" s="146"/>
-      <c r="N2" s="147"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="153"/>
+      <c r="D2" s="153"/>
+      <c r="E2" s="153"/>
+      <c r="F2" s="153"/>
+      <c r="G2" s="153"/>
+      <c r="H2" s="153"/>
+      <c r="I2" s="153"/>
+      <c r="J2" s="153"/>
+      <c r="K2" s="153"/>
+      <c r="L2" s="153"/>
+      <c r="M2" s="153"/>
+      <c r="N2" s="106"/>
     </row>
     <row r="3" spans="1:14" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="67"/>
@@ -4517,1633 +4517,1633 @@
       <c r="M3" s="67"/>
     </row>
     <row r="4" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="148" t="s">
+      <c r="A4" s="154" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="149"/>
-      <c r="C4" s="149"/>
-      <c r="D4" s="149"/>
-      <c r="E4" s="149"/>
-      <c r="F4" s="149"/>
-      <c r="G4" s="149"/>
-      <c r="H4" s="149"/>
-      <c r="I4" s="149"/>
-      <c r="J4" s="149"/>
-      <c r="K4" s="149"/>
-      <c r="L4" s="149"/>
-      <c r="M4" s="150"/>
+      <c r="B4" s="155"/>
+      <c r="C4" s="155"/>
+      <c r="D4" s="155"/>
+      <c r="E4" s="155"/>
+      <c r="F4" s="155"/>
+      <c r="G4" s="155"/>
+      <c r="H4" s="155"/>
+      <c r="I4" s="155"/>
+      <c r="J4" s="155"/>
+      <c r="K4" s="155"/>
+      <c r="L4" s="155"/>
+      <c r="M4" s="156"/>
     </row>
     <row r="5" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="151"/>
-      <c r="B5" s="152"/>
-      <c r="C5" s="152"/>
-      <c r="D5" s="152"/>
-      <c r="E5" s="152"/>
-      <c r="F5" s="152"/>
-      <c r="G5" s="152"/>
-      <c r="H5" s="152"/>
-      <c r="I5" s="152"/>
-      <c r="J5" s="152"/>
-      <c r="K5" s="152"/>
-      <c r="L5" s="152"/>
-      <c r="M5" s="153"/>
+      <c r="A5" s="157"/>
+      <c r="B5" s="158"/>
+      <c r="C5" s="158"/>
+      <c r="D5" s="158"/>
+      <c r="E5" s="158"/>
+      <c r="F5" s="158"/>
+      <c r="G5" s="158"/>
+      <c r="H5" s="158"/>
+      <c r="I5" s="158"/>
+      <c r="J5" s="158"/>
+      <c r="K5" s="158"/>
+      <c r="L5" s="158"/>
+      <c r="M5" s="159"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="154" t="s">
+      <c r="A6" s="160" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="155"/>
-      <c r="C6" s="155"/>
-      <c r="D6" s="155"/>
-      <c r="E6" s="155"/>
-      <c r="F6" s="155"/>
-      <c r="G6" s="155"/>
-      <c r="H6" s="155"/>
-      <c r="I6" s="155"/>
-      <c r="J6" s="155"/>
-      <c r="K6" s="155"/>
-      <c r="L6" s="155"/>
-      <c r="M6" s="156"/>
+      <c r="B6" s="161"/>
+      <c r="C6" s="161"/>
+      <c r="D6" s="161"/>
+      <c r="E6" s="161"/>
+      <c r="F6" s="161"/>
+      <c r="G6" s="161"/>
+      <c r="H6" s="161"/>
+      <c r="I6" s="161"/>
+      <c r="J6" s="161"/>
+      <c r="K6" s="161"/>
+      <c r="L6" s="161"/>
+      <c r="M6" s="162"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="127" t="s">
+      <c r="A7" s="144" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="128"/>
-      <c r="C7" s="128"/>
-      <c r="D7" s="128"/>
-      <c r="E7" s="128"/>
-      <c r="F7" s="128"/>
-      <c r="G7" s="128"/>
-      <c r="H7" s="128"/>
-      <c r="I7" s="128"/>
-      <c r="J7" s="128"/>
-      <c r="K7" s="128"/>
-      <c r="L7" s="128"/>
-      <c r="M7" s="129"/>
+      <c r="B7" s="145"/>
+      <c r="C7" s="145"/>
+      <c r="D7" s="145"/>
+      <c r="E7" s="145"/>
+      <c r="F7" s="145"/>
+      <c r="G7" s="145"/>
+      <c r="H7" s="145"/>
+      <c r="I7" s="145"/>
+      <c r="J7" s="145"/>
+      <c r="K7" s="145"/>
+      <c r="L7" s="145"/>
+      <c r="M7" s="146"/>
     </row>
     <row r="8" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="124" t="s">
+      <c r="A8" s="147" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="125"/>
-      <c r="C8" s="125"/>
-      <c r="D8" s="125"/>
-      <c r="E8" s="125"/>
-      <c r="F8" s="125"/>
-      <c r="G8" s="125"/>
-      <c r="H8" s="125"/>
-      <c r="I8" s="125"/>
-      <c r="J8" s="125"/>
-      <c r="K8" s="125"/>
-      <c r="L8" s="125"/>
-      <c r="M8" s="126"/>
+      <c r="B8" s="148"/>
+      <c r="C8" s="148"/>
+      <c r="D8" s="148"/>
+      <c r="E8" s="148"/>
+      <c r="F8" s="148"/>
+      <c r="G8" s="148"/>
+      <c r="H8" s="148"/>
+      <c r="I8" s="148"/>
+      <c r="J8" s="148"/>
+      <c r="K8" s="148"/>
+      <c r="L8" s="148"/>
+      <c r="M8" s="149"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="127" t="s">
+      <c r="A9" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="128"/>
-      <c r="C9" s="128"/>
-      <c r="D9" s="128"/>
-      <c r="E9" s="128"/>
-      <c r="F9" s="128"/>
-      <c r="G9" s="128"/>
-      <c r="H9" s="128"/>
-      <c r="I9" s="128"/>
-      <c r="J9" s="128"/>
-      <c r="K9" s="128"/>
-      <c r="L9" s="128"/>
-      <c r="M9" s="129"/>
+      <c r="B9" s="145"/>
+      <c r="C9" s="145"/>
+      <c r="D9" s="145"/>
+      <c r="E9" s="145"/>
+      <c r="F9" s="145"/>
+      <c r="G9" s="145"/>
+      <c r="H9" s="145"/>
+      <c r="I9" s="145"/>
+      <c r="J9" s="145"/>
+      <c r="K9" s="145"/>
+      <c r="L9" s="145"/>
+      <c r="M9" s="146"/>
     </row>
     <row r="10" spans="1:14" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="124" t="s">
+      <c r="A10" s="147" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="125"/>
-      <c r="C10" s="125"/>
-      <c r="D10" s="125"/>
-      <c r="E10" s="125"/>
-      <c r="F10" s="125"/>
-      <c r="G10" s="125"/>
-      <c r="H10" s="125"/>
-      <c r="I10" s="125"/>
-      <c r="J10" s="125"/>
-      <c r="K10" s="125"/>
-      <c r="L10" s="125"/>
-      <c r="M10" s="126"/>
+      <c r="B10" s="148"/>
+      <c r="C10" s="148"/>
+      <c r="D10" s="148"/>
+      <c r="E10" s="148"/>
+      <c r="F10" s="148"/>
+      <c r="G10" s="148"/>
+      <c r="H10" s="148"/>
+      <c r="I10" s="148"/>
+      <c r="J10" s="148"/>
+      <c r="K10" s="148"/>
+      <c r="L10" s="148"/>
+      <c r="M10" s="149"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="127" t="s">
+      <c r="A11" s="144" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="128"/>
-      <c r="C11" s="128"/>
-      <c r="D11" s="128"/>
-      <c r="E11" s="128"/>
-      <c r="F11" s="128"/>
-      <c r="G11" s="128"/>
-      <c r="H11" s="128"/>
-      <c r="I11" s="128"/>
-      <c r="J11" s="128"/>
-      <c r="K11" s="128"/>
-      <c r="L11" s="128"/>
-      <c r="M11" s="129"/>
+      <c r="B11" s="145"/>
+      <c r="C11" s="145"/>
+      <c r="D11" s="145"/>
+      <c r="E11" s="145"/>
+      <c r="F11" s="145"/>
+      <c r="G11" s="145"/>
+      <c r="H11" s="145"/>
+      <c r="I11" s="145"/>
+      <c r="J11" s="145"/>
+      <c r="K11" s="145"/>
+      <c r="L11" s="145"/>
+      <c r="M11" s="146"/>
     </row>
     <row r="12" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="144" t="s">
+      <c r="A12" s="150" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="130"/>
-      <c r="C12" s="130"/>
-      <c r="D12" s="130"/>
-      <c r="E12" s="130"/>
-      <c r="F12" s="130"/>
-      <c r="G12" s="130"/>
-      <c r="H12" s="130"/>
-      <c r="I12" s="130"/>
-      <c r="J12" s="130"/>
-      <c r="K12" s="130"/>
-      <c r="L12" s="130"/>
-      <c r="M12" s="145"/>
+      <c r="B12" s="151"/>
+      <c r="C12" s="151"/>
+      <c r="D12" s="151"/>
+      <c r="E12" s="151"/>
+      <c r="F12" s="151"/>
+      <c r="G12" s="151"/>
+      <c r="H12" s="151"/>
+      <c r="I12" s="151"/>
+      <c r="J12" s="151"/>
+      <c r="K12" s="151"/>
+      <c r="L12" s="151"/>
+      <c r="M12" s="152"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="144"/>
-      <c r="B13" s="130"/>
-      <c r="C13" s="130"/>
-      <c r="D13" s="130"/>
-      <c r="E13" s="130"/>
-      <c r="F13" s="130"/>
-      <c r="G13" s="130"/>
-      <c r="H13" s="130"/>
-      <c r="I13" s="130"/>
-      <c r="J13" s="130"/>
-      <c r="K13" s="130"/>
-      <c r="L13" s="130"/>
-      <c r="M13" s="145"/>
+      <c r="A13" s="150"/>
+      <c r="B13" s="151"/>
+      <c r="C13" s="151"/>
+      <c r="D13" s="151"/>
+      <c r="E13" s="151"/>
+      <c r="F13" s="151"/>
+      <c r="G13" s="151"/>
+      <c r="H13" s="151"/>
+      <c r="I13" s="151"/>
+      <c r="J13" s="151"/>
+      <c r="K13" s="151"/>
+      <c r="L13" s="151"/>
+      <c r="M13" s="152"/>
     </row>
     <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="144"/>
-      <c r="B14" s="130"/>
-      <c r="C14" s="130"/>
-      <c r="D14" s="130"/>
-      <c r="E14" s="130"/>
-      <c r="F14" s="130"/>
-      <c r="G14" s="130"/>
-      <c r="H14" s="130"/>
-      <c r="I14" s="130"/>
-      <c r="J14" s="130"/>
-      <c r="K14" s="130"/>
-      <c r="L14" s="130"/>
-      <c r="M14" s="145"/>
+      <c r="A14" s="150"/>
+      <c r="B14" s="151"/>
+      <c r="C14" s="151"/>
+      <c r="D14" s="151"/>
+      <c r="E14" s="151"/>
+      <c r="F14" s="151"/>
+      <c r="G14" s="151"/>
+      <c r="H14" s="151"/>
+      <c r="I14" s="151"/>
+      <c r="J14" s="151"/>
+      <c r="K14" s="151"/>
+      <c r="L14" s="151"/>
+      <c r="M14" s="152"/>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="144"/>
-      <c r="B15" s="130"/>
-      <c r="C15" s="130"/>
-      <c r="D15" s="130"/>
-      <c r="E15" s="130"/>
-      <c r="F15" s="130"/>
-      <c r="G15" s="130"/>
-      <c r="H15" s="130"/>
-      <c r="I15" s="130"/>
-      <c r="J15" s="130"/>
-      <c r="K15" s="130"/>
-      <c r="L15" s="130"/>
-      <c r="M15" s="145"/>
+      <c r="A15" s="150"/>
+      <c r="B15" s="151"/>
+      <c r="C15" s="151"/>
+      <c r="D15" s="151"/>
+      <c r="E15" s="151"/>
+      <c r="F15" s="151"/>
+      <c r="G15" s="151"/>
+      <c r="H15" s="151"/>
+      <c r="I15" s="151"/>
+      <c r="J15" s="151"/>
+      <c r="K15" s="151"/>
+      <c r="L15" s="151"/>
+      <c r="M15" s="152"/>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="144"/>
-      <c r="B16" s="130"/>
-      <c r="C16" s="130"/>
-      <c r="D16" s="130"/>
-      <c r="E16" s="130"/>
-      <c r="F16" s="130"/>
-      <c r="G16" s="130"/>
-      <c r="H16" s="130"/>
-      <c r="I16" s="130"/>
-      <c r="J16" s="130"/>
-      <c r="K16" s="130"/>
-      <c r="L16" s="130"/>
-      <c r="M16" s="145"/>
+      <c r="A16" s="150"/>
+      <c r="B16" s="151"/>
+      <c r="C16" s="151"/>
+      <c r="D16" s="151"/>
+      <c r="E16" s="151"/>
+      <c r="F16" s="151"/>
+      <c r="G16" s="151"/>
+      <c r="H16" s="151"/>
+      <c r="I16" s="151"/>
+      <c r="J16" s="151"/>
+      <c r="K16" s="151"/>
+      <c r="L16" s="151"/>
+      <c r="M16" s="152"/>
     </row>
     <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="144"/>
-      <c r="B17" s="130"/>
-      <c r="C17" s="130"/>
-      <c r="D17" s="130"/>
-      <c r="E17" s="130"/>
-      <c r="F17" s="130"/>
-      <c r="G17" s="130"/>
-      <c r="H17" s="130"/>
-      <c r="I17" s="130"/>
-      <c r="J17" s="130"/>
-      <c r="K17" s="130"/>
-      <c r="L17" s="130"/>
-      <c r="M17" s="145"/>
+      <c r="A17" s="150"/>
+      <c r="B17" s="151"/>
+      <c r="C17" s="151"/>
+      <c r="D17" s="151"/>
+      <c r="E17" s="151"/>
+      <c r="F17" s="151"/>
+      <c r="G17" s="151"/>
+      <c r="H17" s="151"/>
+      <c r="I17" s="151"/>
+      <c r="J17" s="151"/>
+      <c r="K17" s="151"/>
+      <c r="L17" s="151"/>
+      <c r="M17" s="152"/>
     </row>
     <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="144"/>
-      <c r="B18" s="130"/>
-      <c r="C18" s="130"/>
-      <c r="D18" s="130"/>
-      <c r="E18" s="130"/>
-      <c r="F18" s="130"/>
-      <c r="G18" s="130"/>
-      <c r="H18" s="130"/>
-      <c r="I18" s="130"/>
-      <c r="J18" s="130"/>
-      <c r="K18" s="130"/>
-      <c r="L18" s="130"/>
-      <c r="M18" s="145"/>
+      <c r="A18" s="150"/>
+      <c r="B18" s="151"/>
+      <c r="C18" s="151"/>
+      <c r="D18" s="151"/>
+      <c r="E18" s="151"/>
+      <c r="F18" s="151"/>
+      <c r="G18" s="151"/>
+      <c r="H18" s="151"/>
+      <c r="I18" s="151"/>
+      <c r="J18" s="151"/>
+      <c r="K18" s="151"/>
+      <c r="L18" s="151"/>
+      <c r="M18" s="152"/>
     </row>
     <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="144"/>
-      <c r="B19" s="130"/>
-      <c r="C19" s="130"/>
-      <c r="D19" s="130"/>
-      <c r="E19" s="130"/>
-      <c r="F19" s="130"/>
-      <c r="G19" s="130"/>
-      <c r="H19" s="130"/>
-      <c r="I19" s="130"/>
-      <c r="J19" s="130"/>
-      <c r="K19" s="130"/>
-      <c r="L19" s="130"/>
-      <c r="M19" s="145"/>
+      <c r="A19" s="150"/>
+      <c r="B19" s="151"/>
+      <c r="C19" s="151"/>
+      <c r="D19" s="151"/>
+      <c r="E19" s="151"/>
+      <c r="F19" s="151"/>
+      <c r="G19" s="151"/>
+      <c r="H19" s="151"/>
+      <c r="I19" s="151"/>
+      <c r="J19" s="151"/>
+      <c r="K19" s="151"/>
+      <c r="L19" s="151"/>
+      <c r="M19" s="152"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="144"/>
-      <c r="B20" s="130"/>
-      <c r="C20" s="130"/>
-      <c r="D20" s="130"/>
-      <c r="E20" s="130"/>
-      <c r="F20" s="130"/>
-      <c r="G20" s="130"/>
-      <c r="H20" s="130"/>
-      <c r="I20" s="130"/>
-      <c r="J20" s="130"/>
-      <c r="K20" s="130"/>
-      <c r="L20" s="130"/>
-      <c r="M20" s="145"/>
+      <c r="A20" s="150"/>
+      <c r="B20" s="151"/>
+      <c r="C20" s="151"/>
+      <c r="D20" s="151"/>
+      <c r="E20" s="151"/>
+      <c r="F20" s="151"/>
+      <c r="G20" s="151"/>
+      <c r="H20" s="151"/>
+      <c r="I20" s="151"/>
+      <c r="J20" s="151"/>
+      <c r="K20" s="151"/>
+      <c r="L20" s="151"/>
+      <c r="M20" s="152"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="127" t="s">
+      <c r="A21" s="144" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="128"/>
-      <c r="C21" s="128"/>
-      <c r="D21" s="128"/>
-      <c r="E21" s="128"/>
-      <c r="F21" s="128"/>
-      <c r="G21" s="128"/>
-      <c r="H21" s="128"/>
-      <c r="I21" s="128"/>
-      <c r="J21" s="128"/>
-      <c r="K21" s="128"/>
-      <c r="L21" s="128"/>
-      <c r="M21" s="129"/>
+      <c r="B21" s="145"/>
+      <c r="C21" s="145"/>
+      <c r="D21" s="145"/>
+      <c r="E21" s="145"/>
+      <c r="F21" s="145"/>
+      <c r="G21" s="145"/>
+      <c r="H21" s="145"/>
+      <c r="I21" s="145"/>
+      <c r="J21" s="145"/>
+      <c r="K21" s="145"/>
+      <c r="L21" s="145"/>
+      <c r="M21" s="146"/>
     </row>
     <row r="22" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="124" t="s">
+      <c r="A22" s="147" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="125"/>
-      <c r="C22" s="125"/>
-      <c r="D22" s="125"/>
-      <c r="E22" s="125"/>
-      <c r="F22" s="125"/>
-      <c r="G22" s="125"/>
-      <c r="H22" s="125"/>
-      <c r="I22" s="125"/>
-      <c r="J22" s="125"/>
-      <c r="K22" s="125"/>
-      <c r="L22" s="125"/>
-      <c r="M22" s="126"/>
+      <c r="B22" s="148"/>
+      <c r="C22" s="148"/>
+      <c r="D22" s="148"/>
+      <c r="E22" s="148"/>
+      <c r="F22" s="148"/>
+      <c r="G22" s="148"/>
+      <c r="H22" s="148"/>
+      <c r="I22" s="148"/>
+      <c r="J22" s="148"/>
+      <c r="K22" s="148"/>
+      <c r="L22" s="148"/>
+      <c r="M22" s="149"/>
     </row>
     <row r="23" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="124"/>
-      <c r="B23" s="125"/>
-      <c r="C23" s="125"/>
-      <c r="D23" s="125"/>
-      <c r="E23" s="125"/>
-      <c r="F23" s="125"/>
-      <c r="G23" s="125"/>
-      <c r="H23" s="125"/>
-      <c r="I23" s="125"/>
-      <c r="J23" s="125"/>
-      <c r="K23" s="125"/>
-      <c r="L23" s="125"/>
-      <c r="M23" s="126"/>
+      <c r="A23" s="147"/>
+      <c r="B23" s="148"/>
+      <c r="C23" s="148"/>
+      <c r="D23" s="148"/>
+      <c r="E23" s="148"/>
+      <c r="F23" s="148"/>
+      <c r="G23" s="148"/>
+      <c r="H23" s="148"/>
+      <c r="I23" s="148"/>
+      <c r="J23" s="148"/>
+      <c r="K23" s="148"/>
+      <c r="L23" s="148"/>
+      <c r="M23" s="149"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="127" t="s">
+      <c r="A24" s="144" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="128"/>
-      <c r="C24" s="128"/>
-      <c r="D24" s="128"/>
-      <c r="E24" s="128"/>
-      <c r="F24" s="128"/>
-      <c r="G24" s="128"/>
-      <c r="H24" s="128"/>
-      <c r="I24" s="128"/>
-      <c r="J24" s="128"/>
-      <c r="K24" s="128"/>
-      <c r="L24" s="128"/>
-      <c r="M24" s="129"/>
+      <c r="B24" s="145"/>
+      <c r="C24" s="145"/>
+      <c r="D24" s="145"/>
+      <c r="E24" s="145"/>
+      <c r="F24" s="145"/>
+      <c r="G24" s="145"/>
+      <c r="H24" s="145"/>
+      <c r="I24" s="145"/>
+      <c r="J24" s="145"/>
+      <c r="K24" s="145"/>
+      <c r="L24" s="145"/>
+      <c r="M24" s="146"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="141" t="s">
+      <c r="A25" s="163" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="142"/>
-      <c r="C25" s="142"/>
-      <c r="D25" s="142"/>
-      <c r="E25" s="142"/>
-      <c r="F25" s="142"/>
-      <c r="G25" s="142"/>
-      <c r="H25" s="142"/>
-      <c r="I25" s="142"/>
-      <c r="J25" s="142"/>
-      <c r="K25" s="142"/>
-      <c r="L25" s="142"/>
-      <c r="M25" s="143"/>
+      <c r="B25" s="164"/>
+      <c r="C25" s="164"/>
+      <c r="D25" s="164"/>
+      <c r="E25" s="164"/>
+      <c r="F25" s="164"/>
+      <c r="G25" s="164"/>
+      <c r="H25" s="164"/>
+      <c r="I25" s="164"/>
+      <c r="J25" s="164"/>
+      <c r="K25" s="164"/>
+      <c r="L25" s="164"/>
+      <c r="M25" s="165"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="141" t="s">
+      <c r="A26" s="163" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="142"/>
-      <c r="C26" s="142"/>
-      <c r="D26" s="142"/>
-      <c r="E26" s="142"/>
-      <c r="F26" s="142"/>
-      <c r="G26" s="142"/>
-      <c r="H26" s="142"/>
-      <c r="I26" s="142"/>
-      <c r="J26" s="142"/>
-      <c r="K26" s="142"/>
-      <c r="L26" s="142"/>
-      <c r="M26" s="143"/>
+      <c r="B26" s="164"/>
+      <c r="C26" s="164"/>
+      <c r="D26" s="164"/>
+      <c r="E26" s="164"/>
+      <c r="F26" s="164"/>
+      <c r="G26" s="164"/>
+      <c r="H26" s="164"/>
+      <c r="I26" s="164"/>
+      <c r="J26" s="164"/>
+      <c r="K26" s="164"/>
+      <c r="L26" s="164"/>
+      <c r="M26" s="165"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="141" t="s">
+      <c r="A27" s="163" t="s">
         <v>18</v>
       </c>
-      <c r="B27" s="142"/>
-      <c r="C27" s="142"/>
-      <c r="D27" s="142"/>
-      <c r="E27" s="142"/>
-      <c r="F27" s="142"/>
-      <c r="G27" s="142"/>
-      <c r="H27" s="142"/>
-      <c r="I27" s="142"/>
-      <c r="J27" s="142"/>
-      <c r="K27" s="142"/>
-      <c r="L27" s="142"/>
-      <c r="M27" s="143"/>
+      <c r="B27" s="164"/>
+      <c r="C27" s="164"/>
+      <c r="D27" s="164"/>
+      <c r="E27" s="164"/>
+      <c r="F27" s="164"/>
+      <c r="G27" s="164"/>
+      <c r="H27" s="164"/>
+      <c r="I27" s="164"/>
+      <c r="J27" s="164"/>
+      <c r="K27" s="164"/>
+      <c r="L27" s="164"/>
+      <c r="M27" s="165"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="141" t="s">
+      <c r="A28" s="163" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="142"/>
-      <c r="C28" s="142"/>
-      <c r="D28" s="142"/>
-      <c r="E28" s="142"/>
-      <c r="F28" s="142"/>
-      <c r="G28" s="142"/>
-      <c r="H28" s="142"/>
-      <c r="I28" s="142"/>
-      <c r="J28" s="142"/>
-      <c r="K28" s="142"/>
-      <c r="L28" s="142"/>
-      <c r="M28" s="143"/>
+      <c r="B28" s="164"/>
+      <c r="C28" s="164"/>
+      <c r="D28" s="164"/>
+      <c r="E28" s="164"/>
+      <c r="F28" s="164"/>
+      <c r="G28" s="164"/>
+      <c r="H28" s="164"/>
+      <c r="I28" s="164"/>
+      <c r="J28" s="164"/>
+      <c r="K28" s="164"/>
+      <c r="L28" s="164"/>
+      <c r="M28" s="165"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="141" t="s">
+      <c r="A29" s="163" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="142"/>
-      <c r="C29" s="142"/>
-      <c r="D29" s="142"/>
-      <c r="E29" s="142"/>
-      <c r="F29" s="142"/>
-      <c r="G29" s="142"/>
-      <c r="H29" s="142"/>
-      <c r="I29" s="142"/>
-      <c r="J29" s="142"/>
-      <c r="K29" s="142"/>
-      <c r="L29" s="142"/>
-      <c r="M29" s="143"/>
+      <c r="B29" s="164"/>
+      <c r="C29" s="164"/>
+      <c r="D29" s="164"/>
+      <c r="E29" s="164"/>
+      <c r="F29" s="164"/>
+      <c r="G29" s="164"/>
+      <c r="H29" s="164"/>
+      <c r="I29" s="164"/>
+      <c r="J29" s="164"/>
+      <c r="K29" s="164"/>
+      <c r="L29" s="164"/>
+      <c r="M29" s="165"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="141" t="s">
+      <c r="A30" s="163" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="142"/>
-      <c r="C30" s="142"/>
-      <c r="D30" s="142"/>
-      <c r="E30" s="142"/>
-      <c r="F30" s="142"/>
-      <c r="G30" s="142"/>
-      <c r="H30" s="142"/>
-      <c r="I30" s="142"/>
-      <c r="J30" s="142"/>
-      <c r="K30" s="142"/>
-      <c r="L30" s="142"/>
-      <c r="M30" s="143"/>
+      <c r="B30" s="164"/>
+      <c r="C30" s="164"/>
+      <c r="D30" s="164"/>
+      <c r="E30" s="164"/>
+      <c r="F30" s="164"/>
+      <c r="G30" s="164"/>
+      <c r="H30" s="164"/>
+      <c r="I30" s="164"/>
+      <c r="J30" s="164"/>
+      <c r="K30" s="164"/>
+      <c r="L30" s="164"/>
+      <c r="M30" s="165"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="141" t="s">
+      <c r="A31" s="163" t="s">
         <v>22</v>
       </c>
-      <c r="B31" s="142"/>
-      <c r="C31" s="142"/>
-      <c r="D31" s="142"/>
-      <c r="E31" s="142"/>
-      <c r="F31" s="142"/>
-      <c r="G31" s="142"/>
-      <c r="H31" s="142"/>
-      <c r="I31" s="142"/>
-      <c r="J31" s="142"/>
-      <c r="K31" s="142"/>
-      <c r="L31" s="142"/>
-      <c r="M31" s="143"/>
+      <c r="B31" s="164"/>
+      <c r="C31" s="164"/>
+      <c r="D31" s="164"/>
+      <c r="E31" s="164"/>
+      <c r="F31" s="164"/>
+      <c r="G31" s="164"/>
+      <c r="H31" s="164"/>
+      <c r="I31" s="164"/>
+      <c r="J31" s="164"/>
+      <c r="K31" s="164"/>
+      <c r="L31" s="164"/>
+      <c r="M31" s="165"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="141" t="s">
+      <c r="A32" s="163" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="142"/>
-      <c r="C32" s="142"/>
-      <c r="D32" s="142"/>
-      <c r="E32" s="142"/>
-      <c r="F32" s="142"/>
-      <c r="G32" s="142"/>
-      <c r="H32" s="142"/>
-      <c r="I32" s="142"/>
-      <c r="J32" s="142"/>
-      <c r="K32" s="142"/>
-      <c r="L32" s="142"/>
-      <c r="M32" s="143"/>
+      <c r="B32" s="164"/>
+      <c r="C32" s="164"/>
+      <c r="D32" s="164"/>
+      <c r="E32" s="164"/>
+      <c r="F32" s="164"/>
+      <c r="G32" s="164"/>
+      <c r="H32" s="164"/>
+      <c r="I32" s="164"/>
+      <c r="J32" s="164"/>
+      <c r="K32" s="164"/>
+      <c r="L32" s="164"/>
+      <c r="M32" s="165"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="141" t="s">
+      <c r="A33" s="163" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="142"/>
-      <c r="C33" s="142"/>
-      <c r="D33" s="142"/>
-      <c r="E33" s="142"/>
-      <c r="F33" s="142"/>
-      <c r="G33" s="142"/>
-      <c r="H33" s="142"/>
-      <c r="I33" s="142"/>
-      <c r="J33" s="142"/>
-      <c r="K33" s="142"/>
-      <c r="L33" s="142"/>
-      <c r="M33" s="143"/>
+      <c r="B33" s="164"/>
+      <c r="C33" s="164"/>
+      <c r="D33" s="164"/>
+      <c r="E33" s="164"/>
+      <c r="F33" s="164"/>
+      <c r="G33" s="164"/>
+      <c r="H33" s="164"/>
+      <c r="I33" s="164"/>
+      <c r="J33" s="164"/>
+      <c r="K33" s="164"/>
+      <c r="L33" s="164"/>
+      <c r="M33" s="165"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="141" t="s">
+      <c r="A34" s="163" t="s">
         <v>25</v>
       </c>
-      <c r="B34" s="142"/>
-      <c r="C34" s="142"/>
-      <c r="D34" s="142"/>
-      <c r="E34" s="142"/>
-      <c r="F34" s="142"/>
-      <c r="G34" s="142"/>
-      <c r="H34" s="142"/>
-      <c r="I34" s="142"/>
-      <c r="J34" s="142"/>
-      <c r="K34" s="142"/>
-      <c r="L34" s="142"/>
-      <c r="M34" s="143"/>
+      <c r="B34" s="164"/>
+      <c r="C34" s="164"/>
+      <c r="D34" s="164"/>
+      <c r="E34" s="164"/>
+      <c r="F34" s="164"/>
+      <c r="G34" s="164"/>
+      <c r="H34" s="164"/>
+      <c r="I34" s="164"/>
+      <c r="J34" s="164"/>
+      <c r="K34" s="164"/>
+      <c r="L34" s="164"/>
+      <c r="M34" s="165"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="141" t="s">
+      <c r="A35" s="163" t="s">
         <v>26</v>
       </c>
-      <c r="B35" s="142"/>
-      <c r="C35" s="142"/>
-      <c r="D35" s="142"/>
-      <c r="E35" s="142"/>
-      <c r="F35" s="142"/>
-      <c r="G35" s="142"/>
-      <c r="H35" s="142"/>
-      <c r="I35" s="142"/>
-      <c r="J35" s="142"/>
-      <c r="K35" s="142"/>
-      <c r="L35" s="142"/>
-      <c r="M35" s="143"/>
+      <c r="B35" s="164"/>
+      <c r="C35" s="164"/>
+      <c r="D35" s="164"/>
+      <c r="E35" s="164"/>
+      <c r="F35" s="164"/>
+      <c r="G35" s="164"/>
+      <c r="H35" s="164"/>
+      <c r="I35" s="164"/>
+      <c r="J35" s="164"/>
+      <c r="K35" s="164"/>
+      <c r="L35" s="164"/>
+      <c r="M35" s="165"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="141" t="s">
+      <c r="A36" s="163" t="s">
         <v>27</v>
       </c>
-      <c r="B36" s="142"/>
-      <c r="C36" s="142"/>
-      <c r="D36" s="142"/>
-      <c r="E36" s="142"/>
-      <c r="F36" s="142"/>
-      <c r="G36" s="142"/>
-      <c r="H36" s="142"/>
-      <c r="I36" s="142"/>
-      <c r="J36" s="142"/>
-      <c r="K36" s="142"/>
-      <c r="L36" s="142"/>
-      <c r="M36" s="143"/>
+      <c r="B36" s="164"/>
+      <c r="C36" s="164"/>
+      <c r="D36" s="164"/>
+      <c r="E36" s="164"/>
+      <c r="F36" s="164"/>
+      <c r="G36" s="164"/>
+      <c r="H36" s="164"/>
+      <c r="I36" s="164"/>
+      <c r="J36" s="164"/>
+      <c r="K36" s="164"/>
+      <c r="L36" s="164"/>
+      <c r="M36" s="165"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" s="141" t="s">
+      <c r="A37" s="163" t="s">
         <v>28</v>
       </c>
-      <c r="B37" s="142"/>
-      <c r="C37" s="142"/>
-      <c r="D37" s="142"/>
-      <c r="E37" s="142"/>
-      <c r="F37" s="142"/>
-      <c r="G37" s="142"/>
-      <c r="H37" s="142"/>
-      <c r="I37" s="142"/>
-      <c r="J37" s="142"/>
-      <c r="K37" s="142"/>
-      <c r="L37" s="142"/>
-      <c r="M37" s="143"/>
+      <c r="B37" s="164"/>
+      <c r="C37" s="164"/>
+      <c r="D37" s="164"/>
+      <c r="E37" s="164"/>
+      <c r="F37" s="164"/>
+      <c r="G37" s="164"/>
+      <c r="H37" s="164"/>
+      <c r="I37" s="164"/>
+      <c r="J37" s="164"/>
+      <c r="K37" s="164"/>
+      <c r="L37" s="164"/>
+      <c r="M37" s="165"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" s="141" t="s">
+      <c r="A38" s="163" t="s">
         <v>29</v>
       </c>
-      <c r="B38" s="142"/>
-      <c r="C38" s="142"/>
-      <c r="D38" s="142"/>
-      <c r="E38" s="142"/>
-      <c r="F38" s="142"/>
-      <c r="G38" s="142"/>
-      <c r="H38" s="142"/>
-      <c r="I38" s="142"/>
-      <c r="J38" s="142"/>
-      <c r="K38" s="142"/>
-      <c r="L38" s="142"/>
-      <c r="M38" s="143"/>
+      <c r="B38" s="164"/>
+      <c r="C38" s="164"/>
+      <c r="D38" s="164"/>
+      <c r="E38" s="164"/>
+      <c r="F38" s="164"/>
+      <c r="G38" s="164"/>
+      <c r="H38" s="164"/>
+      <c r="I38" s="164"/>
+      <c r="J38" s="164"/>
+      <c r="K38" s="164"/>
+      <c r="L38" s="164"/>
+      <c r="M38" s="165"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" s="141" t="s">
+      <c r="A39" s="163" t="s">
         <v>30</v>
       </c>
-      <c r="B39" s="142"/>
-      <c r="C39" s="142"/>
-      <c r="D39" s="142"/>
-      <c r="E39" s="142"/>
-      <c r="F39" s="142"/>
-      <c r="G39" s="142"/>
-      <c r="H39" s="142"/>
-      <c r="I39" s="142"/>
-      <c r="J39" s="142"/>
-      <c r="K39" s="142"/>
-      <c r="L39" s="142"/>
-      <c r="M39" s="143"/>
+      <c r="B39" s="164"/>
+      <c r="C39" s="164"/>
+      <c r="D39" s="164"/>
+      <c r="E39" s="164"/>
+      <c r="F39" s="164"/>
+      <c r="G39" s="164"/>
+      <c r="H39" s="164"/>
+      <c r="I39" s="164"/>
+      <c r="J39" s="164"/>
+      <c r="K39" s="164"/>
+      <c r="L39" s="164"/>
+      <c r="M39" s="165"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="141" t="s">
+      <c r="A40" s="163" t="s">
         <v>31</v>
       </c>
-      <c r="B40" s="142"/>
-      <c r="C40" s="142"/>
-      <c r="D40" s="142"/>
-      <c r="E40" s="142"/>
-      <c r="F40" s="142"/>
-      <c r="G40" s="142"/>
-      <c r="H40" s="142"/>
-      <c r="I40" s="142"/>
-      <c r="J40" s="142"/>
-      <c r="K40" s="142"/>
-      <c r="L40" s="142"/>
-      <c r="M40" s="143"/>
+      <c r="B40" s="164"/>
+      <c r="C40" s="164"/>
+      <c r="D40" s="164"/>
+      <c r="E40" s="164"/>
+      <c r="F40" s="164"/>
+      <c r="G40" s="164"/>
+      <c r="H40" s="164"/>
+      <c r="I40" s="164"/>
+      <c r="J40" s="164"/>
+      <c r="K40" s="164"/>
+      <c r="L40" s="164"/>
+      <c r="M40" s="165"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="141" t="s">
+      <c r="A41" s="163" t="s">
         <v>32</v>
       </c>
-      <c r="B41" s="142"/>
-      <c r="C41" s="142"/>
-      <c r="D41" s="142"/>
-      <c r="E41" s="142"/>
-      <c r="F41" s="142"/>
-      <c r="G41" s="142"/>
-      <c r="H41" s="142"/>
-      <c r="I41" s="142"/>
-      <c r="J41" s="142"/>
-      <c r="K41" s="142"/>
-      <c r="L41" s="142"/>
-      <c r="M41" s="143"/>
+      <c r="B41" s="164"/>
+      <c r="C41" s="164"/>
+      <c r="D41" s="164"/>
+      <c r="E41" s="164"/>
+      <c r="F41" s="164"/>
+      <c r="G41" s="164"/>
+      <c r="H41" s="164"/>
+      <c r="I41" s="164"/>
+      <c r="J41" s="164"/>
+      <c r="K41" s="164"/>
+      <c r="L41" s="164"/>
+      <c r="M41" s="165"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A42" s="141" t="s">
+      <c r="A42" s="163" t="s">
         <v>33</v>
       </c>
-      <c r="B42" s="142"/>
-      <c r="C42" s="142"/>
-      <c r="D42" s="142"/>
-      <c r="E42" s="142"/>
-      <c r="F42" s="142"/>
-      <c r="G42" s="142"/>
-      <c r="H42" s="142"/>
-      <c r="I42" s="142"/>
-      <c r="J42" s="142"/>
-      <c r="K42" s="142"/>
-      <c r="L42" s="142"/>
-      <c r="M42" s="143"/>
+      <c r="B42" s="164"/>
+      <c r="C42" s="164"/>
+      <c r="D42" s="164"/>
+      <c r="E42" s="164"/>
+      <c r="F42" s="164"/>
+      <c r="G42" s="164"/>
+      <c r="H42" s="164"/>
+      <c r="I42" s="164"/>
+      <c r="J42" s="164"/>
+      <c r="K42" s="164"/>
+      <c r="L42" s="164"/>
+      <c r="M42" s="165"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="141" t="s">
+      <c r="A43" s="163" t="s">
         <v>34</v>
       </c>
-      <c r="B43" s="142"/>
-      <c r="C43" s="142"/>
-      <c r="D43" s="142"/>
-      <c r="E43" s="142"/>
-      <c r="F43" s="142"/>
-      <c r="G43" s="142"/>
-      <c r="H43" s="142"/>
-      <c r="I43" s="142"/>
-      <c r="J43" s="142"/>
-      <c r="K43" s="142"/>
-      <c r="L43" s="142"/>
-      <c r="M43" s="143"/>
+      <c r="B43" s="164"/>
+      <c r="C43" s="164"/>
+      <c r="D43" s="164"/>
+      <c r="E43" s="164"/>
+      <c r="F43" s="164"/>
+      <c r="G43" s="164"/>
+      <c r="H43" s="164"/>
+      <c r="I43" s="164"/>
+      <c r="J43" s="164"/>
+      <c r="K43" s="164"/>
+      <c r="L43" s="164"/>
+      <c r="M43" s="165"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" s="141" t="s">
+      <c r="A44" s="163" t="s">
         <v>35</v>
       </c>
-      <c r="B44" s="142"/>
-      <c r="C44" s="142"/>
-      <c r="D44" s="142"/>
-      <c r="E44" s="142"/>
-      <c r="F44" s="142"/>
-      <c r="G44" s="142"/>
-      <c r="H44" s="142"/>
-      <c r="I44" s="142"/>
-      <c r="J44" s="142"/>
-      <c r="K44" s="142"/>
-      <c r="L44" s="142"/>
-      <c r="M44" s="143"/>
+      <c r="B44" s="164"/>
+      <c r="C44" s="164"/>
+      <c r="D44" s="164"/>
+      <c r="E44" s="164"/>
+      <c r="F44" s="164"/>
+      <c r="G44" s="164"/>
+      <c r="H44" s="164"/>
+      <c r="I44" s="164"/>
+      <c r="J44" s="164"/>
+      <c r="K44" s="164"/>
+      <c r="L44" s="164"/>
+      <c r="M44" s="165"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A45" s="141" t="s">
+      <c r="A45" s="163" t="s">
         <v>36</v>
       </c>
-      <c r="B45" s="142"/>
-      <c r="C45" s="142"/>
-      <c r="D45" s="142"/>
-      <c r="E45" s="142"/>
-      <c r="F45" s="142"/>
-      <c r="G45" s="142"/>
-      <c r="H45" s="142"/>
-      <c r="I45" s="142"/>
-      <c r="J45" s="142"/>
-      <c r="K45" s="142"/>
-      <c r="L45" s="142"/>
-      <c r="M45" s="143"/>
+      <c r="B45" s="164"/>
+      <c r="C45" s="164"/>
+      <c r="D45" s="164"/>
+      <c r="E45" s="164"/>
+      <c r="F45" s="164"/>
+      <c r="G45" s="164"/>
+      <c r="H45" s="164"/>
+      <c r="I45" s="164"/>
+      <c r="J45" s="164"/>
+      <c r="K45" s="164"/>
+      <c r="L45" s="164"/>
+      <c r="M45" s="165"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A46" s="141" t="s">
+      <c r="A46" s="163" t="s">
         <v>37</v>
       </c>
-      <c r="B46" s="142"/>
-      <c r="C46" s="142"/>
-      <c r="D46" s="142"/>
-      <c r="E46" s="142"/>
-      <c r="F46" s="142"/>
-      <c r="G46" s="142"/>
-      <c r="H46" s="142"/>
-      <c r="I46" s="142"/>
-      <c r="J46" s="142"/>
-      <c r="K46" s="142"/>
-      <c r="L46" s="142"/>
-      <c r="M46" s="143"/>
+      <c r="B46" s="164"/>
+      <c r="C46" s="164"/>
+      <c r="D46" s="164"/>
+      <c r="E46" s="164"/>
+      <c r="F46" s="164"/>
+      <c r="G46" s="164"/>
+      <c r="H46" s="164"/>
+      <c r="I46" s="164"/>
+      <c r="J46" s="164"/>
+      <c r="K46" s="164"/>
+      <c r="L46" s="164"/>
+      <c r="M46" s="165"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A47" s="141" t="s">
+      <c r="A47" s="163" t="s">
         <v>38</v>
       </c>
-      <c r="B47" s="142"/>
-      <c r="C47" s="142"/>
-      <c r="D47" s="142"/>
-      <c r="E47" s="142"/>
-      <c r="F47" s="142"/>
-      <c r="G47" s="142"/>
-      <c r="H47" s="142"/>
-      <c r="I47" s="142"/>
-      <c r="J47" s="142"/>
-      <c r="K47" s="142"/>
-      <c r="L47" s="142"/>
-      <c r="M47" s="143"/>
+      <c r="B47" s="164"/>
+      <c r="C47" s="164"/>
+      <c r="D47" s="164"/>
+      <c r="E47" s="164"/>
+      <c r="F47" s="164"/>
+      <c r="G47" s="164"/>
+      <c r="H47" s="164"/>
+      <c r="I47" s="164"/>
+      <c r="J47" s="164"/>
+      <c r="K47" s="164"/>
+      <c r="L47" s="164"/>
+      <c r="M47" s="165"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="141" t="s">
+      <c r="A48" s="163" t="s">
         <v>39</v>
       </c>
-      <c r="B48" s="142"/>
-      <c r="C48" s="142"/>
-      <c r="D48" s="142"/>
-      <c r="E48" s="142"/>
-      <c r="F48" s="142"/>
-      <c r="G48" s="142"/>
-      <c r="H48" s="142"/>
-      <c r="I48" s="142"/>
-      <c r="J48" s="142"/>
-      <c r="K48" s="142"/>
-      <c r="L48" s="142"/>
-      <c r="M48" s="143"/>
+      <c r="B48" s="164"/>
+      <c r="C48" s="164"/>
+      <c r="D48" s="164"/>
+      <c r="E48" s="164"/>
+      <c r="F48" s="164"/>
+      <c r="G48" s="164"/>
+      <c r="H48" s="164"/>
+      <c r="I48" s="164"/>
+      <c r="J48" s="164"/>
+      <c r="K48" s="164"/>
+      <c r="L48" s="164"/>
+      <c r="M48" s="165"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A49" s="141" t="s">
+      <c r="A49" s="163" t="s">
         <v>40</v>
       </c>
-      <c r="B49" s="142"/>
-      <c r="C49" s="142"/>
-      <c r="D49" s="142"/>
-      <c r="E49" s="142"/>
-      <c r="F49" s="142"/>
-      <c r="G49" s="142"/>
-      <c r="H49" s="142"/>
-      <c r="I49" s="142"/>
-      <c r="J49" s="142"/>
-      <c r="K49" s="142"/>
-      <c r="L49" s="142"/>
-      <c r="M49" s="143"/>
+      <c r="B49" s="164"/>
+      <c r="C49" s="164"/>
+      <c r="D49" s="164"/>
+      <c r="E49" s="164"/>
+      <c r="F49" s="164"/>
+      <c r="G49" s="164"/>
+      <c r="H49" s="164"/>
+      <c r="I49" s="164"/>
+      <c r="J49" s="164"/>
+      <c r="K49" s="164"/>
+      <c r="L49" s="164"/>
+      <c r="M49" s="165"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A50" s="141" t="s">
+      <c r="A50" s="163" t="s">
         <v>41</v>
       </c>
-      <c r="B50" s="142"/>
-      <c r="C50" s="142"/>
-      <c r="D50" s="142"/>
-      <c r="E50" s="142"/>
-      <c r="F50" s="142"/>
-      <c r="G50" s="142"/>
-      <c r="H50" s="142"/>
-      <c r="I50" s="142"/>
-      <c r="J50" s="142"/>
-      <c r="K50" s="142"/>
-      <c r="L50" s="142"/>
-      <c r="M50" s="143"/>
+      <c r="B50" s="164"/>
+      <c r="C50" s="164"/>
+      <c r="D50" s="164"/>
+      <c r="E50" s="164"/>
+      <c r="F50" s="164"/>
+      <c r="G50" s="164"/>
+      <c r="H50" s="164"/>
+      <c r="I50" s="164"/>
+      <c r="J50" s="164"/>
+      <c r="K50" s="164"/>
+      <c r="L50" s="164"/>
+      <c r="M50" s="165"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A51" s="141" t="s">
+      <c r="A51" s="163" t="s">
         <v>42</v>
       </c>
-      <c r="B51" s="142"/>
-      <c r="C51" s="142"/>
-      <c r="D51" s="142"/>
-      <c r="E51" s="142"/>
-      <c r="F51" s="142"/>
-      <c r="G51" s="142"/>
-      <c r="H51" s="142"/>
-      <c r="I51" s="142"/>
-      <c r="J51" s="142"/>
-      <c r="K51" s="142"/>
-      <c r="L51" s="142"/>
-      <c r="M51" s="143"/>
+      <c r="B51" s="164"/>
+      <c r="C51" s="164"/>
+      <c r="D51" s="164"/>
+      <c r="E51" s="164"/>
+      <c r="F51" s="164"/>
+      <c r="G51" s="164"/>
+      <c r="H51" s="164"/>
+      <c r="I51" s="164"/>
+      <c r="J51" s="164"/>
+      <c r="K51" s="164"/>
+      <c r="L51" s="164"/>
+      <c r="M51" s="165"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A52" s="141" t="s">
+      <c r="A52" s="163" t="s">
         <v>43</v>
       </c>
-      <c r="B52" s="142"/>
-      <c r="C52" s="142"/>
-      <c r="D52" s="142"/>
-      <c r="E52" s="142"/>
-      <c r="F52" s="142"/>
-      <c r="G52" s="142"/>
-      <c r="H52" s="142"/>
-      <c r="I52" s="142"/>
-      <c r="J52" s="142"/>
-      <c r="K52" s="142"/>
-      <c r="L52" s="142"/>
-      <c r="M52" s="143"/>
+      <c r="B52" s="164"/>
+      <c r="C52" s="164"/>
+      <c r="D52" s="164"/>
+      <c r="E52" s="164"/>
+      <c r="F52" s="164"/>
+      <c r="G52" s="164"/>
+      <c r="H52" s="164"/>
+      <c r="I52" s="164"/>
+      <c r="J52" s="164"/>
+      <c r="K52" s="164"/>
+      <c r="L52" s="164"/>
+      <c r="M52" s="165"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A53" s="141" t="s">
+      <c r="A53" s="163" t="s">
         <v>44</v>
       </c>
-      <c r="B53" s="142"/>
-      <c r="C53" s="142"/>
-      <c r="D53" s="142"/>
-      <c r="E53" s="142"/>
-      <c r="F53" s="142"/>
-      <c r="G53" s="142"/>
-      <c r="H53" s="142"/>
-      <c r="I53" s="142"/>
-      <c r="J53" s="142"/>
-      <c r="K53" s="142"/>
-      <c r="L53" s="142"/>
-      <c r="M53" s="143"/>
+      <c r="B53" s="164"/>
+      <c r="C53" s="164"/>
+      <c r="D53" s="164"/>
+      <c r="E53" s="164"/>
+      <c r="F53" s="164"/>
+      <c r="G53" s="164"/>
+      <c r="H53" s="164"/>
+      <c r="I53" s="164"/>
+      <c r="J53" s="164"/>
+      <c r="K53" s="164"/>
+      <c r="L53" s="164"/>
+      <c r="M53" s="165"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A54" s="141" t="s">
+      <c r="A54" s="163" t="s">
         <v>45</v>
       </c>
-      <c r="B54" s="142"/>
-      <c r="C54" s="142"/>
-      <c r="D54" s="142"/>
-      <c r="E54" s="142"/>
-      <c r="F54" s="142"/>
-      <c r="G54" s="142"/>
-      <c r="H54" s="142"/>
-      <c r="I54" s="142"/>
-      <c r="J54" s="142"/>
-      <c r="K54" s="142"/>
-      <c r="L54" s="142"/>
-      <c r="M54" s="143"/>
+      <c r="B54" s="164"/>
+      <c r="C54" s="164"/>
+      <c r="D54" s="164"/>
+      <c r="E54" s="164"/>
+      <c r="F54" s="164"/>
+      <c r="G54" s="164"/>
+      <c r="H54" s="164"/>
+      <c r="I54" s="164"/>
+      <c r="J54" s="164"/>
+      <c r="K54" s="164"/>
+      <c r="L54" s="164"/>
+      <c r="M54" s="165"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A55" s="141" t="s">
+      <c r="A55" s="163" t="s">
         <v>46</v>
       </c>
-      <c r="B55" s="142"/>
-      <c r="C55" s="142"/>
-      <c r="D55" s="142"/>
-      <c r="E55" s="142"/>
-      <c r="F55" s="142"/>
-      <c r="G55" s="142"/>
-      <c r="H55" s="142"/>
-      <c r="I55" s="142"/>
-      <c r="J55" s="142"/>
-      <c r="K55" s="142"/>
-      <c r="L55" s="142"/>
-      <c r="M55" s="143"/>
+      <c r="B55" s="164"/>
+      <c r="C55" s="164"/>
+      <c r="D55" s="164"/>
+      <c r="E55" s="164"/>
+      <c r="F55" s="164"/>
+      <c r="G55" s="164"/>
+      <c r="H55" s="164"/>
+      <c r="I55" s="164"/>
+      <c r="J55" s="164"/>
+      <c r="K55" s="164"/>
+      <c r="L55" s="164"/>
+      <c r="M55" s="165"/>
     </row>
     <row r="56" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="141" t="s">
+      <c r="A56" s="163" t="s">
         <v>47</v>
       </c>
-      <c r="B56" s="142"/>
-      <c r="C56" s="142"/>
-      <c r="D56" s="142"/>
-      <c r="E56" s="142"/>
-      <c r="F56" s="142"/>
-      <c r="G56" s="142"/>
-      <c r="H56" s="142"/>
-      <c r="I56" s="142"/>
-      <c r="J56" s="142"/>
-      <c r="K56" s="142"/>
-      <c r="L56" s="142"/>
-      <c r="M56" s="143"/>
+      <c r="B56" s="164"/>
+      <c r="C56" s="164"/>
+      <c r="D56" s="164"/>
+      <c r="E56" s="164"/>
+      <c r="F56" s="164"/>
+      <c r="G56" s="164"/>
+      <c r="H56" s="164"/>
+      <c r="I56" s="164"/>
+      <c r="J56" s="164"/>
+      <c r="K56" s="164"/>
+      <c r="L56" s="164"/>
+      <c r="M56" s="165"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A57" s="141" t="s">
+      <c r="A57" s="163" t="s">
         <v>48</v>
       </c>
-      <c r="B57" s="142"/>
-      <c r="C57" s="142"/>
-      <c r="D57" s="142"/>
-      <c r="E57" s="142"/>
-      <c r="F57" s="142"/>
-      <c r="G57" s="142"/>
-      <c r="H57" s="142"/>
-      <c r="I57" s="142"/>
-      <c r="J57" s="142"/>
-      <c r="K57" s="142"/>
-      <c r="L57" s="142"/>
-      <c r="M57" s="143"/>
+      <c r="B57" s="164"/>
+      <c r="C57" s="164"/>
+      <c r="D57" s="164"/>
+      <c r="E57" s="164"/>
+      <c r="F57" s="164"/>
+      <c r="G57" s="164"/>
+      <c r="H57" s="164"/>
+      <c r="I57" s="164"/>
+      <c r="J57" s="164"/>
+      <c r="K57" s="164"/>
+      <c r="L57" s="164"/>
+      <c r="M57" s="165"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A58" s="141" t="s">
+      <c r="A58" s="163" t="s">
         <v>49</v>
       </c>
-      <c r="B58" s="142"/>
-      <c r="C58" s="142"/>
-      <c r="D58" s="142"/>
-      <c r="E58" s="142"/>
-      <c r="F58" s="142"/>
-      <c r="G58" s="142"/>
-      <c r="H58" s="142"/>
-      <c r="I58" s="142"/>
-      <c r="J58" s="142"/>
-      <c r="K58" s="142"/>
-      <c r="L58" s="142"/>
-      <c r="M58" s="143"/>
+      <c r="B58" s="164"/>
+      <c r="C58" s="164"/>
+      <c r="D58" s="164"/>
+      <c r="E58" s="164"/>
+      <c r="F58" s="164"/>
+      <c r="G58" s="164"/>
+      <c r="H58" s="164"/>
+      <c r="I58" s="164"/>
+      <c r="J58" s="164"/>
+      <c r="K58" s="164"/>
+      <c r="L58" s="164"/>
+      <c r="M58" s="165"/>
     </row>
     <row r="59" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="141" t="s">
+      <c r="A59" s="163" t="s">
         <v>50</v>
       </c>
-      <c r="B59" s="142"/>
-      <c r="C59" s="142"/>
-      <c r="D59" s="142"/>
-      <c r="E59" s="142"/>
-      <c r="F59" s="142"/>
-      <c r="G59" s="142"/>
-      <c r="H59" s="142"/>
-      <c r="I59" s="142"/>
-      <c r="J59" s="142"/>
-      <c r="K59" s="142"/>
-      <c r="L59" s="142"/>
-      <c r="M59" s="143"/>
+      <c r="B59" s="164"/>
+      <c r="C59" s="164"/>
+      <c r="D59" s="164"/>
+      <c r="E59" s="164"/>
+      <c r="F59" s="164"/>
+      <c r="G59" s="164"/>
+      <c r="H59" s="164"/>
+      <c r="I59" s="164"/>
+      <c r="J59" s="164"/>
+      <c r="K59" s="164"/>
+      <c r="L59" s="164"/>
+      <c r="M59" s="165"/>
     </row>
     <row r="60" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="141" t="s">
+      <c r="A60" s="163" t="s">
         <v>51</v>
       </c>
-      <c r="B60" s="142"/>
-      <c r="C60" s="142"/>
-      <c r="D60" s="142"/>
-      <c r="E60" s="142"/>
-      <c r="F60" s="142"/>
-      <c r="G60" s="142"/>
-      <c r="H60" s="142"/>
-      <c r="I60" s="142"/>
-      <c r="J60" s="142"/>
-      <c r="K60" s="142"/>
-      <c r="L60" s="142"/>
-      <c r="M60" s="143"/>
+      <c r="B60" s="164"/>
+      <c r="C60" s="164"/>
+      <c r="D60" s="164"/>
+      <c r="E60" s="164"/>
+      <c r="F60" s="164"/>
+      <c r="G60" s="164"/>
+      <c r="H60" s="164"/>
+      <c r="I60" s="164"/>
+      <c r="J60" s="164"/>
+      <c r="K60" s="164"/>
+      <c r="L60" s="164"/>
+      <c r="M60" s="165"/>
     </row>
     <row r="61" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="141" t="s">
+      <c r="A61" s="163" t="s">
         <v>52</v>
       </c>
-      <c r="B61" s="142"/>
-      <c r="C61" s="142"/>
-      <c r="D61" s="142"/>
-      <c r="E61" s="142"/>
-      <c r="F61" s="142"/>
-      <c r="G61" s="142"/>
-      <c r="H61" s="142"/>
-      <c r="I61" s="142"/>
-      <c r="J61" s="142"/>
-      <c r="K61" s="142"/>
-      <c r="L61" s="142"/>
-      <c r="M61" s="143"/>
+      <c r="B61" s="164"/>
+      <c r="C61" s="164"/>
+      <c r="D61" s="164"/>
+      <c r="E61" s="164"/>
+      <c r="F61" s="164"/>
+      <c r="G61" s="164"/>
+      <c r="H61" s="164"/>
+      <c r="I61" s="164"/>
+      <c r="J61" s="164"/>
+      <c r="K61" s="164"/>
+      <c r="L61" s="164"/>
+      <c r="M61" s="165"/>
     </row>
     <row r="62" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="141" t="s">
+      <c r="A62" s="163" t="s">
         <v>53</v>
       </c>
-      <c r="B62" s="142"/>
-      <c r="C62" s="142"/>
-      <c r="D62" s="142"/>
-      <c r="E62" s="142"/>
-      <c r="F62" s="142"/>
-      <c r="G62" s="142"/>
-      <c r="H62" s="142"/>
-      <c r="I62" s="142"/>
-      <c r="J62" s="142"/>
-      <c r="K62" s="142"/>
-      <c r="L62" s="142"/>
-      <c r="M62" s="143"/>
+      <c r="B62" s="164"/>
+      <c r="C62" s="164"/>
+      <c r="D62" s="164"/>
+      <c r="E62" s="164"/>
+      <c r="F62" s="164"/>
+      <c r="G62" s="164"/>
+      <c r="H62" s="164"/>
+      <c r="I62" s="164"/>
+      <c r="J62" s="164"/>
+      <c r="K62" s="164"/>
+      <c r="L62" s="164"/>
+      <c r="M62" s="165"/>
     </row>
     <row r="63" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="141" t="s">
+      <c r="A63" s="163" t="s">
         <v>54</v>
       </c>
-      <c r="B63" s="142"/>
-      <c r="C63" s="142"/>
-      <c r="D63" s="142"/>
-      <c r="E63" s="142"/>
-      <c r="F63" s="142"/>
-      <c r="G63" s="142"/>
-      <c r="H63" s="142"/>
-      <c r="I63" s="142"/>
-      <c r="J63" s="142"/>
-      <c r="K63" s="142"/>
-      <c r="L63" s="142"/>
-      <c r="M63" s="143"/>
+      <c r="B63" s="164"/>
+      <c r="C63" s="164"/>
+      <c r="D63" s="164"/>
+      <c r="E63" s="164"/>
+      <c r="F63" s="164"/>
+      <c r="G63" s="164"/>
+      <c r="H63" s="164"/>
+      <c r="I63" s="164"/>
+      <c r="J63" s="164"/>
+      <c r="K63" s="164"/>
+      <c r="L63" s="164"/>
+      <c r="M63" s="165"/>
     </row>
     <row r="64" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="141" t="s">
+      <c r="A64" s="163" t="s">
         <v>55</v>
       </c>
-      <c r="B64" s="142"/>
-      <c r="C64" s="142"/>
-      <c r="D64" s="142"/>
-      <c r="E64" s="142"/>
-      <c r="F64" s="142"/>
-      <c r="G64" s="142"/>
-      <c r="H64" s="142"/>
-      <c r="I64" s="142"/>
-      <c r="J64" s="142"/>
-      <c r="K64" s="142"/>
-      <c r="L64" s="142"/>
-      <c r="M64" s="143"/>
+      <c r="B64" s="164"/>
+      <c r="C64" s="164"/>
+      <c r="D64" s="164"/>
+      <c r="E64" s="164"/>
+      <c r="F64" s="164"/>
+      <c r="G64" s="164"/>
+      <c r="H64" s="164"/>
+      <c r="I64" s="164"/>
+      <c r="J64" s="164"/>
+      <c r="K64" s="164"/>
+      <c r="L64" s="164"/>
+      <c r="M64" s="165"/>
     </row>
     <row r="65" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="141" t="s">
+      <c r="A65" s="163" t="s">
         <v>56</v>
       </c>
-      <c r="B65" s="142"/>
-      <c r="C65" s="142"/>
-      <c r="D65" s="142"/>
-      <c r="E65" s="142"/>
-      <c r="F65" s="142"/>
-      <c r="G65" s="142"/>
-      <c r="H65" s="142"/>
-      <c r="I65" s="142"/>
-      <c r="J65" s="142"/>
-      <c r="K65" s="142"/>
-      <c r="L65" s="142"/>
-      <c r="M65" s="143"/>
+      <c r="B65" s="164"/>
+      <c r="C65" s="164"/>
+      <c r="D65" s="164"/>
+      <c r="E65" s="164"/>
+      <c r="F65" s="164"/>
+      <c r="G65" s="164"/>
+      <c r="H65" s="164"/>
+      <c r="I65" s="164"/>
+      <c r="J65" s="164"/>
+      <c r="K65" s="164"/>
+      <c r="L65" s="164"/>
+      <c r="M65" s="165"/>
     </row>
     <row r="66" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="141" t="s">
+      <c r="A66" s="163" t="s">
         <v>57</v>
       </c>
-      <c r="B66" s="142"/>
-      <c r="C66" s="142"/>
-      <c r="D66" s="142"/>
-      <c r="E66" s="142"/>
-      <c r="F66" s="142"/>
-      <c r="G66" s="142"/>
-      <c r="H66" s="142"/>
-      <c r="I66" s="142"/>
-      <c r="J66" s="142"/>
-      <c r="K66" s="142"/>
-      <c r="L66" s="142"/>
-      <c r="M66" s="143"/>
+      <c r="B66" s="164"/>
+      <c r="C66" s="164"/>
+      <c r="D66" s="164"/>
+      <c r="E66" s="164"/>
+      <c r="F66" s="164"/>
+      <c r="G66" s="164"/>
+      <c r="H66" s="164"/>
+      <c r="I66" s="164"/>
+      <c r="J66" s="164"/>
+      <c r="K66" s="164"/>
+      <c r="L66" s="164"/>
+      <c r="M66" s="165"/>
     </row>
     <row r="67" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="141" t="s">
+      <c r="A67" s="163" t="s">
         <v>58</v>
       </c>
-      <c r="B67" s="142"/>
-      <c r="C67" s="142"/>
-      <c r="D67" s="142"/>
-      <c r="E67" s="142"/>
-      <c r="F67" s="142"/>
-      <c r="G67" s="142"/>
-      <c r="H67" s="142"/>
-      <c r="I67" s="142"/>
-      <c r="J67" s="142"/>
-      <c r="K67" s="142"/>
-      <c r="L67" s="142"/>
-      <c r="M67" s="143"/>
+      <c r="B67" s="164"/>
+      <c r="C67" s="164"/>
+      <c r="D67" s="164"/>
+      <c r="E67" s="164"/>
+      <c r="F67" s="164"/>
+      <c r="G67" s="164"/>
+      <c r="H67" s="164"/>
+      <c r="I67" s="164"/>
+      <c r="J67" s="164"/>
+      <c r="K67" s="164"/>
+      <c r="L67" s="164"/>
+      <c r="M67" s="165"/>
     </row>
     <row r="68" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="141" t="s">
+      <c r="A68" s="163" t="s">
         <v>59</v>
       </c>
-      <c r="B68" s="142"/>
-      <c r="C68" s="142"/>
-      <c r="D68" s="142"/>
-      <c r="E68" s="142"/>
-      <c r="F68" s="142"/>
-      <c r="G68" s="142"/>
-      <c r="H68" s="142"/>
-      <c r="I68" s="142"/>
-      <c r="J68" s="142"/>
-      <c r="K68" s="142"/>
-      <c r="L68" s="142"/>
-      <c r="M68" s="143"/>
+      <c r="B68" s="164"/>
+      <c r="C68" s="164"/>
+      <c r="D68" s="164"/>
+      <c r="E68" s="164"/>
+      <c r="F68" s="164"/>
+      <c r="G68" s="164"/>
+      <c r="H68" s="164"/>
+      <c r="I68" s="164"/>
+      <c r="J68" s="164"/>
+      <c r="K68" s="164"/>
+      <c r="L68" s="164"/>
+      <c r="M68" s="165"/>
     </row>
     <row r="69" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="141" t="s">
+      <c r="A69" s="163" t="s">
         <v>60</v>
       </c>
-      <c r="B69" s="142"/>
-      <c r="C69" s="142"/>
-      <c r="D69" s="142"/>
-      <c r="E69" s="142"/>
-      <c r="F69" s="142"/>
-      <c r="G69" s="142"/>
-      <c r="H69" s="142"/>
-      <c r="I69" s="142"/>
-      <c r="J69" s="142"/>
-      <c r="K69" s="142"/>
-      <c r="L69" s="142"/>
-      <c r="M69" s="143"/>
+      <c r="B69" s="164"/>
+      <c r="C69" s="164"/>
+      <c r="D69" s="164"/>
+      <c r="E69" s="164"/>
+      <c r="F69" s="164"/>
+      <c r="G69" s="164"/>
+      <c r="H69" s="164"/>
+      <c r="I69" s="164"/>
+      <c r="J69" s="164"/>
+      <c r="K69" s="164"/>
+      <c r="L69" s="164"/>
+      <c r="M69" s="165"/>
     </row>
     <row r="70" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="127" t="s">
+      <c r="A70" s="144" t="s">
         <v>61</v>
       </c>
-      <c r="B70" s="128"/>
-      <c r="C70" s="128"/>
-      <c r="D70" s="128"/>
-      <c r="E70" s="128"/>
-      <c r="F70" s="128"/>
-      <c r="G70" s="128"/>
-      <c r="H70" s="128"/>
-      <c r="I70" s="128"/>
-      <c r="J70" s="128"/>
-      <c r="K70" s="128"/>
-      <c r="L70" s="128"/>
-      <c r="M70" s="129"/>
+      <c r="B70" s="145"/>
+      <c r="C70" s="145"/>
+      <c r="D70" s="145"/>
+      <c r="E70" s="145"/>
+      <c r="F70" s="145"/>
+      <c r="G70" s="145"/>
+      <c r="H70" s="145"/>
+      <c r="I70" s="145"/>
+      <c r="J70" s="145"/>
+      <c r="K70" s="145"/>
+      <c r="L70" s="145"/>
+      <c r="M70" s="146"/>
     </row>
     <row r="71" spans="1:13" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="144" t="s">
+      <c r="A71" s="150" t="s">
         <v>62</v>
       </c>
-      <c r="B71" s="130"/>
-      <c r="C71" s="130"/>
-      <c r="D71" s="130"/>
-      <c r="E71" s="130"/>
-      <c r="F71" s="130"/>
-      <c r="G71" s="130"/>
-      <c r="H71" s="130"/>
-      <c r="I71" s="130"/>
-      <c r="J71" s="130"/>
-      <c r="K71" s="130"/>
-      <c r="L71" s="130"/>
-      <c r="M71" s="145"/>
+      <c r="B71" s="151"/>
+      <c r="C71" s="151"/>
+      <c r="D71" s="151"/>
+      <c r="E71" s="151"/>
+      <c r="F71" s="151"/>
+      <c r="G71" s="151"/>
+      <c r="H71" s="151"/>
+      <c r="I71" s="151"/>
+      <c r="J71" s="151"/>
+      <c r="K71" s="151"/>
+      <c r="L71" s="151"/>
+      <c r="M71" s="152"/>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A72" s="127" t="s">
+      <c r="A72" s="144" t="s">
         <v>63</v>
       </c>
-      <c r="B72" s="128"/>
-      <c r="C72" s="128"/>
-      <c r="D72" s="128"/>
-      <c r="E72" s="128"/>
-      <c r="F72" s="128"/>
-      <c r="G72" s="128"/>
-      <c r="H72" s="128"/>
-      <c r="I72" s="128"/>
-      <c r="J72" s="128"/>
-      <c r="K72" s="128"/>
-      <c r="L72" s="128"/>
-      <c r="M72" s="129"/>
+      <c r="B72" s="145"/>
+      <c r="C72" s="145"/>
+      <c r="D72" s="145"/>
+      <c r="E72" s="145"/>
+      <c r="F72" s="145"/>
+      <c r="G72" s="145"/>
+      <c r="H72" s="145"/>
+      <c r="I72" s="145"/>
+      <c r="J72" s="145"/>
+      <c r="K72" s="145"/>
+      <c r="L72" s="145"/>
+      <c r="M72" s="146"/>
     </row>
     <row r="73" spans="1:13" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="124" t="s">
+      <c r="A73" s="147" t="s">
         <v>64</v>
       </c>
-      <c r="B73" s="125"/>
-      <c r="C73" s="125"/>
-      <c r="D73" s="125"/>
-      <c r="E73" s="125"/>
-      <c r="F73" s="125"/>
-      <c r="G73" s="125"/>
-      <c r="H73" s="125"/>
-      <c r="I73" s="125"/>
-      <c r="J73" s="125"/>
-      <c r="K73" s="125"/>
-      <c r="L73" s="125"/>
-      <c r="M73" s="126"/>
+      <c r="B73" s="148"/>
+      <c r="C73" s="148"/>
+      <c r="D73" s="148"/>
+      <c r="E73" s="148"/>
+      <c r="F73" s="148"/>
+      <c r="G73" s="148"/>
+      <c r="H73" s="148"/>
+      <c r="I73" s="148"/>
+      <c r="J73" s="148"/>
+      <c r="K73" s="148"/>
+      <c r="L73" s="148"/>
+      <c r="M73" s="149"/>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A74" s="127" t="s">
+      <c r="A74" s="144" t="s">
         <v>65</v>
       </c>
-      <c r="B74" s="128"/>
-      <c r="C74" s="128"/>
-      <c r="D74" s="128"/>
-      <c r="E74" s="128"/>
-      <c r="F74" s="128"/>
-      <c r="G74" s="128"/>
-      <c r="H74" s="128"/>
-      <c r="I74" s="128"/>
-      <c r="J74" s="128"/>
-      <c r="K74" s="128"/>
-      <c r="L74" s="128"/>
-      <c r="M74" s="129"/>
+      <c r="B74" s="145"/>
+      <c r="C74" s="145"/>
+      <c r="D74" s="145"/>
+      <c r="E74" s="145"/>
+      <c r="F74" s="145"/>
+      <c r="G74" s="145"/>
+      <c r="H74" s="145"/>
+      <c r="I74" s="145"/>
+      <c r="J74" s="145"/>
+      <c r="K74" s="145"/>
+      <c r="L74" s="145"/>
+      <c r="M74" s="146"/>
     </row>
     <row r="75" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="124" t="s">
+      <c r="A75" s="147" t="s">
         <v>66</v>
       </c>
-      <c r="B75" s="125"/>
-      <c r="C75" s="125"/>
-      <c r="D75" s="125"/>
-      <c r="E75" s="125"/>
-      <c r="F75" s="125"/>
-      <c r="G75" s="125"/>
-      <c r="H75" s="125"/>
-      <c r="I75" s="125"/>
-      <c r="J75" s="125"/>
-      <c r="K75" s="125"/>
-      <c r="L75" s="125"/>
-      <c r="M75" s="126"/>
+      <c r="B75" s="148"/>
+      <c r="C75" s="148"/>
+      <c r="D75" s="148"/>
+      <c r="E75" s="148"/>
+      <c r="F75" s="148"/>
+      <c r="G75" s="148"/>
+      <c r="H75" s="148"/>
+      <c r="I75" s="148"/>
+      <c r="J75" s="148"/>
+      <c r="K75" s="148"/>
+      <c r="L75" s="148"/>
+      <c r="M75" s="149"/>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A76" s="127" t="s">
+      <c r="A76" s="144" t="s">
         <v>67</v>
       </c>
-      <c r="B76" s="128"/>
-      <c r="C76" s="128"/>
-      <c r="D76" s="128"/>
-      <c r="E76" s="128"/>
-      <c r="F76" s="128"/>
-      <c r="G76" s="128"/>
-      <c r="H76" s="128"/>
-      <c r="I76" s="128"/>
-      <c r="J76" s="128"/>
-      <c r="K76" s="128"/>
-      <c r="L76" s="128"/>
-      <c r="M76" s="129"/>
+      <c r="B76" s="145"/>
+      <c r="C76" s="145"/>
+      <c r="D76" s="145"/>
+      <c r="E76" s="145"/>
+      <c r="F76" s="145"/>
+      <c r="G76" s="145"/>
+      <c r="H76" s="145"/>
+      <c r="I76" s="145"/>
+      <c r="J76" s="145"/>
+      <c r="K76" s="145"/>
+      <c r="L76" s="145"/>
+      <c r="M76" s="146"/>
     </row>
     <row r="77" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="136" t="s">
+      <c r="A77" s="166" t="s">
         <v>68</v>
       </c>
-      <c r="B77" s="125"/>
-      <c r="C77" s="125"/>
-      <c r="D77" s="125"/>
-      <c r="E77" s="125"/>
-      <c r="F77" s="125"/>
-      <c r="G77" s="125"/>
-      <c r="H77" s="125"/>
-      <c r="I77" s="125"/>
-      <c r="J77" s="125"/>
-      <c r="K77" s="125"/>
-      <c r="L77" s="125"/>
-      <c r="M77" s="126"/>
+      <c r="B77" s="148"/>
+      <c r="C77" s="148"/>
+      <c r="D77" s="148"/>
+      <c r="E77" s="148"/>
+      <c r="F77" s="148"/>
+      <c r="G77" s="148"/>
+      <c r="H77" s="148"/>
+      <c r="I77" s="148"/>
+      <c r="J77" s="148"/>
+      <c r="K77" s="148"/>
+      <c r="L77" s="148"/>
+      <c r="M77" s="149"/>
     </row>
     <row r="78" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="136" t="s">
+      <c r="A78" s="166" t="s">
         <v>69</v>
       </c>
-      <c r="B78" s="125"/>
-      <c r="C78" s="125"/>
-      <c r="D78" s="125"/>
-      <c r="E78" s="125"/>
-      <c r="F78" s="125"/>
-      <c r="G78" s="125"/>
-      <c r="H78" s="125"/>
-      <c r="I78" s="125"/>
-      <c r="J78" s="125"/>
-      <c r="K78" s="125"/>
-      <c r="L78" s="125"/>
-      <c r="M78" s="126"/>
+      <c r="B78" s="148"/>
+      <c r="C78" s="148"/>
+      <c r="D78" s="148"/>
+      <c r="E78" s="148"/>
+      <c r="F78" s="148"/>
+      <c r="G78" s="148"/>
+      <c r="H78" s="148"/>
+      <c r="I78" s="148"/>
+      <c r="J78" s="148"/>
+      <c r="K78" s="148"/>
+      <c r="L78" s="148"/>
+      <c r="M78" s="149"/>
     </row>
     <row r="79" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="136" t="s">
+      <c r="A79" s="166" t="s">
         <v>70</v>
       </c>
-      <c r="B79" s="125"/>
-      <c r="C79" s="125"/>
-      <c r="D79" s="125"/>
-      <c r="E79" s="125"/>
-      <c r="F79" s="125"/>
-      <c r="G79" s="125"/>
-      <c r="H79" s="125"/>
-      <c r="I79" s="125"/>
-      <c r="J79" s="125"/>
-      <c r="K79" s="125"/>
-      <c r="L79" s="125"/>
-      <c r="M79" s="126"/>
+      <c r="B79" s="148"/>
+      <c r="C79" s="148"/>
+      <c r="D79" s="148"/>
+      <c r="E79" s="148"/>
+      <c r="F79" s="148"/>
+      <c r="G79" s="148"/>
+      <c r="H79" s="148"/>
+      <c r="I79" s="148"/>
+      <c r="J79" s="148"/>
+      <c r="K79" s="148"/>
+      <c r="L79" s="148"/>
+      <c r="M79" s="149"/>
     </row>
     <row r="80" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="136" t="s">
+      <c r="A80" s="166" t="s">
         <v>71</v>
       </c>
-      <c r="B80" s="125"/>
-      <c r="C80" s="125"/>
-      <c r="D80" s="125"/>
-      <c r="E80" s="125"/>
-      <c r="F80" s="125"/>
-      <c r="G80" s="125"/>
-      <c r="H80" s="125"/>
-      <c r="I80" s="125"/>
-      <c r="J80" s="125"/>
-      <c r="K80" s="125"/>
-      <c r="L80" s="125"/>
-      <c r="M80" s="126"/>
+      <c r="B80" s="148"/>
+      <c r="C80" s="148"/>
+      <c r="D80" s="148"/>
+      <c r="E80" s="148"/>
+      <c r="F80" s="148"/>
+      <c r="G80" s="148"/>
+      <c r="H80" s="148"/>
+      <c r="I80" s="148"/>
+      <c r="J80" s="148"/>
+      <c r="K80" s="148"/>
+      <c r="L80" s="148"/>
+      <c r="M80" s="149"/>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A81" s="127" t="s">
+      <c r="A81" s="144" t="s">
         <v>72</v>
       </c>
-      <c r="B81" s="128"/>
-      <c r="C81" s="128"/>
-      <c r="D81" s="128"/>
-      <c r="E81" s="128"/>
-      <c r="F81" s="128"/>
-      <c r="G81" s="128"/>
-      <c r="H81" s="128"/>
-      <c r="I81" s="128"/>
-      <c r="J81" s="128"/>
-      <c r="K81" s="128"/>
-      <c r="L81" s="128"/>
-      <c r="M81" s="129"/>
+      <c r="B81" s="145"/>
+      <c r="C81" s="145"/>
+      <c r="D81" s="145"/>
+      <c r="E81" s="145"/>
+      <c r="F81" s="145"/>
+      <c r="G81" s="145"/>
+      <c r="H81" s="145"/>
+      <c r="I81" s="145"/>
+      <c r="J81" s="145"/>
+      <c r="K81" s="145"/>
+      <c r="L81" s="145"/>
+      <c r="M81" s="146"/>
     </row>
     <row r="82" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="124" t="s">
+      <c r="A82" s="147" t="s">
         <v>73</v>
       </c>
-      <c r="B82" s="125"/>
-      <c r="C82" s="125"/>
-      <c r="D82" s="125"/>
-      <c r="E82" s="125"/>
-      <c r="F82" s="125"/>
-      <c r="G82" s="125"/>
-      <c r="H82" s="125"/>
-      <c r="I82" s="125"/>
-      <c r="J82" s="125"/>
-      <c r="K82" s="125"/>
-      <c r="L82" s="125"/>
-      <c r="M82" s="126"/>
+      <c r="B82" s="148"/>
+      <c r="C82" s="148"/>
+      <c r="D82" s="148"/>
+      <c r="E82" s="148"/>
+      <c r="F82" s="148"/>
+      <c r="G82" s="148"/>
+      <c r="H82" s="148"/>
+      <c r="I82" s="148"/>
+      <c r="J82" s="148"/>
+      <c r="K82" s="148"/>
+      <c r="L82" s="148"/>
+      <c r="M82" s="149"/>
     </row>
     <row r="83" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="127" t="s">
+      <c r="A83" s="144" t="s">
         <v>74</v>
       </c>
-      <c r="B83" s="128"/>
-      <c r="C83" s="128"/>
-      <c r="D83" s="128"/>
-      <c r="E83" s="128"/>
-      <c r="F83" s="128"/>
-      <c r="G83" s="128"/>
-      <c r="H83" s="128"/>
-      <c r="I83" s="128"/>
-      <c r="J83" s="128"/>
-      <c r="K83" s="128"/>
-      <c r="L83" s="128"/>
-      <c r="M83" s="129"/>
+      <c r="B83" s="145"/>
+      <c r="C83" s="145"/>
+      <c r="D83" s="145"/>
+      <c r="E83" s="145"/>
+      <c r="F83" s="145"/>
+      <c r="G83" s="145"/>
+      <c r="H83" s="145"/>
+      <c r="I83" s="145"/>
+      <c r="J83" s="145"/>
+      <c r="K83" s="145"/>
+      <c r="L83" s="145"/>
+      <c r="M83" s="146"/>
     </row>
     <row r="84" spans="1:13" s="14" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="124" t="s">
+      <c r="A84" s="147" t="s">
         <v>75</v>
       </c>
-      <c r="B84" s="125"/>
-      <c r="C84" s="125"/>
-      <c r="D84" s="125"/>
-      <c r="E84" s="125"/>
-      <c r="F84" s="125"/>
-      <c r="G84" s="125"/>
-      <c r="H84" s="125"/>
-      <c r="I84" s="125"/>
-      <c r="J84" s="125"/>
-      <c r="K84" s="125"/>
-      <c r="L84" s="125"/>
-      <c r="M84" s="126"/>
+      <c r="B84" s="148"/>
+      <c r="C84" s="148"/>
+      <c r="D84" s="148"/>
+      <c r="E84" s="148"/>
+      <c r="F84" s="148"/>
+      <c r="G84" s="148"/>
+      <c r="H84" s="148"/>
+      <c r="I84" s="148"/>
+      <c r="J84" s="148"/>
+      <c r="K84" s="148"/>
+      <c r="L84" s="148"/>
+      <c r="M84" s="149"/>
     </row>
     <row r="85" spans="1:13" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="127" t="s">
+      <c r="A85" s="144" t="s">
         <v>76</v>
       </c>
-      <c r="B85" s="128"/>
-      <c r="C85" s="128"/>
-      <c r="D85" s="128"/>
-      <c r="E85" s="128"/>
-      <c r="F85" s="128"/>
-      <c r="G85" s="128"/>
-      <c r="H85" s="128"/>
-      <c r="I85" s="128"/>
-      <c r="J85" s="128"/>
-      <c r="K85" s="128"/>
-      <c r="L85" s="128"/>
-      <c r="M85" s="129"/>
+      <c r="B85" s="145"/>
+      <c r="C85" s="145"/>
+      <c r="D85" s="145"/>
+      <c r="E85" s="145"/>
+      <c r="F85" s="145"/>
+      <c r="G85" s="145"/>
+      <c r="H85" s="145"/>
+      <c r="I85" s="145"/>
+      <c r="J85" s="145"/>
+      <c r="K85" s="145"/>
+      <c r="L85" s="145"/>
+      <c r="M85" s="146"/>
     </row>
     <row r="86" spans="1:13" s="14" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="124" t="s">
+      <c r="A86" s="147" t="s">
         <v>159</v>
       </c>
-      <c r="B86" s="125"/>
-      <c r="C86" s="125"/>
-      <c r="D86" s="125"/>
-      <c r="E86" s="125"/>
-      <c r="F86" s="125"/>
-      <c r="G86" s="125"/>
-      <c r="H86" s="125"/>
-      <c r="I86" s="125"/>
-      <c r="J86" s="125"/>
-      <c r="K86" s="125"/>
-      <c r="L86" s="125"/>
-      <c r="M86" s="126"/>
+      <c r="B86" s="148"/>
+      <c r="C86" s="148"/>
+      <c r="D86" s="148"/>
+      <c r="E86" s="148"/>
+      <c r="F86" s="148"/>
+      <c r="G86" s="148"/>
+      <c r="H86" s="148"/>
+      <c r="I86" s="148"/>
+      <c r="J86" s="148"/>
+      <c r="K86" s="148"/>
+      <c r="L86" s="148"/>
+      <c r="M86" s="149"/>
     </row>
     <row r="87" spans="1:13" s="14" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="124" t="s">
+      <c r="A87" s="147" t="s">
         <v>77</v>
       </c>
-      <c r="B87" s="125"/>
-      <c r="C87" s="125"/>
-      <c r="D87" s="125"/>
-      <c r="E87" s="125"/>
-      <c r="F87" s="125"/>
-      <c r="G87" s="125"/>
-      <c r="H87" s="125"/>
-      <c r="I87" s="125"/>
-      <c r="J87" s="125"/>
-      <c r="K87" s="125"/>
-      <c r="L87" s="125"/>
-      <c r="M87" s="126"/>
+      <c r="B87" s="148"/>
+      <c r="C87" s="148"/>
+      <c r="D87" s="148"/>
+      <c r="E87" s="148"/>
+      <c r="F87" s="148"/>
+      <c r="G87" s="148"/>
+      <c r="H87" s="148"/>
+      <c r="I87" s="148"/>
+      <c r="J87" s="148"/>
+      <c r="K87" s="148"/>
+      <c r="L87" s="148"/>
+      <c r="M87" s="149"/>
     </row>
     <row r="88" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="127" t="s">
+      <c r="A88" s="144" t="s">
         <v>78</v>
       </c>
-      <c r="B88" s="128"/>
-      <c r="C88" s="128"/>
-      <c r="D88" s="128"/>
-      <c r="E88" s="128"/>
-      <c r="F88" s="128"/>
-      <c r="G88" s="128"/>
-      <c r="H88" s="128"/>
-      <c r="I88" s="128"/>
-      <c r="J88" s="128"/>
-      <c r="K88" s="128"/>
-      <c r="L88" s="128"/>
-      <c r="M88" s="129"/>
+      <c r="B88" s="145"/>
+      <c r="C88" s="145"/>
+      <c r="D88" s="145"/>
+      <c r="E88" s="145"/>
+      <c r="F88" s="145"/>
+      <c r="G88" s="145"/>
+      <c r="H88" s="145"/>
+      <c r="I88" s="145"/>
+      <c r="J88" s="145"/>
+      <c r="K88" s="145"/>
+      <c r="L88" s="145"/>
+      <c r="M88" s="146"/>
     </row>
     <row r="89" spans="1:13" s="14" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="124" t="s">
+      <c r="A89" s="147" t="s">
         <v>79</v>
       </c>
-      <c r="B89" s="125"/>
-      <c r="C89" s="125"/>
-      <c r="D89" s="125"/>
-      <c r="E89" s="125"/>
-      <c r="F89" s="125"/>
-      <c r="G89" s="125"/>
-      <c r="H89" s="125"/>
-      <c r="I89" s="125"/>
-      <c r="J89" s="125"/>
-      <c r="K89" s="125"/>
-      <c r="L89" s="125"/>
-      <c r="M89" s="126"/>
+      <c r="B89" s="148"/>
+      <c r="C89" s="148"/>
+      <c r="D89" s="148"/>
+      <c r="E89" s="148"/>
+      <c r="F89" s="148"/>
+      <c r="G89" s="148"/>
+      <c r="H89" s="148"/>
+      <c r="I89" s="148"/>
+      <c r="J89" s="148"/>
+      <c r="K89" s="148"/>
+      <c r="L89" s="148"/>
+      <c r="M89" s="149"/>
     </row>
     <row r="90" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="127" t="s">
+      <c r="A90" s="144" t="s">
         <v>80</v>
       </c>
-      <c r="B90" s="128"/>
-      <c r="C90" s="128"/>
-      <c r="D90" s="128"/>
-      <c r="E90" s="128"/>
-      <c r="F90" s="128"/>
-      <c r="G90" s="128"/>
-      <c r="H90" s="128"/>
-      <c r="I90" s="128"/>
-      <c r="J90" s="128"/>
-      <c r="K90" s="128"/>
-      <c r="L90" s="128"/>
-      <c r="M90" s="129"/>
+      <c r="B90" s="145"/>
+      <c r="C90" s="145"/>
+      <c r="D90" s="145"/>
+      <c r="E90" s="145"/>
+      <c r="F90" s="145"/>
+      <c r="G90" s="145"/>
+      <c r="H90" s="145"/>
+      <c r="I90" s="145"/>
+      <c r="J90" s="145"/>
+      <c r="K90" s="145"/>
+      <c r="L90" s="145"/>
+      <c r="M90" s="146"/>
     </row>
     <row r="91" spans="1:13" s="14" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="124" t="s">
+      <c r="A91" s="147" t="s">
         <v>81</v>
       </c>
-      <c r="B91" s="125"/>
-      <c r="C91" s="125"/>
-      <c r="D91" s="125"/>
-      <c r="E91" s="125"/>
-      <c r="F91" s="125"/>
-      <c r="G91" s="125"/>
-      <c r="H91" s="125"/>
-      <c r="I91" s="125"/>
-      <c r="J91" s="125"/>
-      <c r="K91" s="125"/>
-      <c r="L91" s="125"/>
-      <c r="M91" s="126"/>
+      <c r="B91" s="148"/>
+      <c r="C91" s="148"/>
+      <c r="D91" s="148"/>
+      <c r="E91" s="148"/>
+      <c r="F91" s="148"/>
+      <c r="G91" s="148"/>
+      <c r="H91" s="148"/>
+      <c r="I91" s="148"/>
+      <c r="J91" s="148"/>
+      <c r="K91" s="148"/>
+      <c r="L91" s="148"/>
+      <c r="M91" s="149"/>
     </row>
     <row r="92" spans="1:13" s="14" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="124" t="s">
+      <c r="A92" s="147" t="s">
         <v>82</v>
       </c>
-      <c r="B92" s="125"/>
-      <c r="C92" s="125"/>
-      <c r="D92" s="125"/>
-      <c r="E92" s="125"/>
-      <c r="F92" s="125"/>
-      <c r="G92" s="125"/>
-      <c r="H92" s="125"/>
-      <c r="I92" s="125"/>
-      <c r="J92" s="125"/>
-      <c r="K92" s="125"/>
-      <c r="L92" s="125"/>
-      <c r="M92" s="126"/>
+      <c r="B92" s="148"/>
+      <c r="C92" s="148"/>
+      <c r="D92" s="148"/>
+      <c r="E92" s="148"/>
+      <c r="F92" s="148"/>
+      <c r="G92" s="148"/>
+      <c r="H92" s="148"/>
+      <c r="I92" s="148"/>
+      <c r="J92" s="148"/>
+      <c r="K92" s="148"/>
+      <c r="L92" s="148"/>
+      <c r="M92" s="149"/>
     </row>
     <row r="93" spans="1:13" s="14" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="124" t="s">
+      <c r="A93" s="147" t="s">
         <v>83</v>
       </c>
-      <c r="B93" s="125"/>
-      <c r="C93" s="125"/>
-      <c r="D93" s="125"/>
-      <c r="E93" s="125"/>
-      <c r="F93" s="125"/>
-      <c r="G93" s="125"/>
-      <c r="H93" s="125"/>
-      <c r="I93" s="125"/>
-      <c r="J93" s="125"/>
-      <c r="K93" s="125"/>
-      <c r="L93" s="125"/>
-      <c r="M93" s="126"/>
+      <c r="B93" s="148"/>
+      <c r="C93" s="148"/>
+      <c r="D93" s="148"/>
+      <c r="E93" s="148"/>
+      <c r="F93" s="148"/>
+      <c r="G93" s="148"/>
+      <c r="H93" s="148"/>
+      <c r="I93" s="148"/>
+      <c r="J93" s="148"/>
+      <c r="K93" s="148"/>
+      <c r="L93" s="148"/>
+      <c r="M93" s="149"/>
     </row>
     <row r="94" spans="1:13" s="14" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="124" t="s">
+      <c r="A94" s="147" t="s">
         <v>84</v>
       </c>
-      <c r="B94" s="125"/>
-      <c r="C94" s="125"/>
-      <c r="D94" s="125"/>
-      <c r="E94" s="125"/>
-      <c r="F94" s="125"/>
-      <c r="G94" s="125"/>
-      <c r="H94" s="125"/>
-      <c r="I94" s="125"/>
-      <c r="J94" s="125"/>
-      <c r="K94" s="125"/>
-      <c r="L94" s="125"/>
-      <c r="M94" s="126"/>
+      <c r="B94" s="148"/>
+      <c r="C94" s="148"/>
+      <c r="D94" s="148"/>
+      <c r="E94" s="148"/>
+      <c r="F94" s="148"/>
+      <c r="G94" s="148"/>
+      <c r="H94" s="148"/>
+      <c r="I94" s="148"/>
+      <c r="J94" s="148"/>
+      <c r="K94" s="148"/>
+      <c r="L94" s="148"/>
+      <c r="M94" s="149"/>
     </row>
     <row r="95" spans="1:13" s="14" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="124" t="s">
+      <c r="A95" s="147" t="s">
         <v>85</v>
       </c>
-      <c r="B95" s="125"/>
-      <c r="C95" s="125"/>
-      <c r="D95" s="125"/>
-      <c r="E95" s="125"/>
-      <c r="F95" s="125"/>
-      <c r="G95" s="125"/>
-      <c r="H95" s="125"/>
-      <c r="I95" s="125"/>
-      <c r="J95" s="125"/>
-      <c r="K95" s="125"/>
-      <c r="L95" s="125"/>
-      <c r="M95" s="126"/>
+      <c r="B95" s="148"/>
+      <c r="C95" s="148"/>
+      <c r="D95" s="148"/>
+      <c r="E95" s="148"/>
+      <c r="F95" s="148"/>
+      <c r="G95" s="148"/>
+      <c r="H95" s="148"/>
+      <c r="I95" s="148"/>
+      <c r="J95" s="148"/>
+      <c r="K95" s="148"/>
+      <c r="L95" s="148"/>
+      <c r="M95" s="149"/>
     </row>
     <row r="96" spans="1:13" s="14" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="124" t="s">
+      <c r="A96" s="147" t="s">
         <v>86</v>
       </c>
-      <c r="B96" s="125"/>
-      <c r="C96" s="125"/>
-      <c r="D96" s="125"/>
-      <c r="E96" s="125"/>
-      <c r="F96" s="125"/>
-      <c r="G96" s="125"/>
-      <c r="H96" s="125"/>
-      <c r="I96" s="125"/>
-      <c r="J96" s="125"/>
-      <c r="K96" s="125"/>
-      <c r="L96" s="125"/>
-      <c r="M96" s="126"/>
+      <c r="B96" s="148"/>
+      <c r="C96" s="148"/>
+      <c r="D96" s="148"/>
+      <c r="E96" s="148"/>
+      <c r="F96" s="148"/>
+      <c r="G96" s="148"/>
+      <c r="H96" s="148"/>
+      <c r="I96" s="148"/>
+      <c r="J96" s="148"/>
+      <c r="K96" s="148"/>
+      <c r="L96" s="148"/>
+      <c r="M96" s="149"/>
     </row>
     <row r="97" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="127" t="s">
+      <c r="A97" s="144" t="s">
         <v>87</v>
       </c>
-      <c r="B97" s="128"/>
-      <c r="C97" s="128"/>
-      <c r="D97" s="128"/>
-      <c r="E97" s="128"/>
-      <c r="F97" s="128"/>
-      <c r="G97" s="128"/>
-      <c r="H97" s="128"/>
-      <c r="I97" s="128"/>
-      <c r="J97" s="128"/>
-      <c r="K97" s="128"/>
-      <c r="L97" s="128"/>
-      <c r="M97" s="129"/>
+      <c r="B97" s="145"/>
+      <c r="C97" s="145"/>
+      <c r="D97" s="145"/>
+      <c r="E97" s="145"/>
+      <c r="F97" s="145"/>
+      <c r="G97" s="145"/>
+      <c r="H97" s="145"/>
+      <c r="I97" s="145"/>
+      <c r="J97" s="145"/>
+      <c r="K97" s="145"/>
+      <c r="L97" s="145"/>
+      <c r="M97" s="146"/>
     </row>
     <row r="98" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="124" t="s">
+      <c r="A98" s="147" t="s">
         <v>88</v>
       </c>
-      <c r="B98" s="125"/>
-      <c r="C98" s="125"/>
-      <c r="D98" s="125"/>
-      <c r="E98" s="125"/>
-      <c r="F98" s="125"/>
-      <c r="G98" s="125"/>
-      <c r="H98" s="125"/>
-      <c r="I98" s="125"/>
-      <c r="J98" s="125"/>
-      <c r="K98" s="125"/>
-      <c r="L98" s="125"/>
-      <c r="M98" s="126"/>
+      <c r="B98" s="148"/>
+      <c r="C98" s="148"/>
+      <c r="D98" s="148"/>
+      <c r="E98" s="148"/>
+      <c r="F98" s="148"/>
+      <c r="G98" s="148"/>
+      <c r="H98" s="148"/>
+      <c r="I98" s="148"/>
+      <c r="J98" s="148"/>
+      <c r="K98" s="148"/>
+      <c r="L98" s="148"/>
+      <c r="M98" s="149"/>
     </row>
     <row r="99" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="127" t="s">
+      <c r="A99" s="144" t="s">
         <v>89</v>
       </c>
-      <c r="B99" s="128"/>
-      <c r="C99" s="128"/>
-      <c r="D99" s="128"/>
-      <c r="E99" s="128"/>
-      <c r="F99" s="128"/>
-      <c r="G99" s="128"/>
-      <c r="H99" s="128"/>
-      <c r="I99" s="128"/>
-      <c r="J99" s="128"/>
-      <c r="K99" s="128"/>
-      <c r="L99" s="128"/>
-      <c r="M99" s="129"/>
+      <c r="B99" s="145"/>
+      <c r="C99" s="145"/>
+      <c r="D99" s="145"/>
+      <c r="E99" s="145"/>
+      <c r="F99" s="145"/>
+      <c r="G99" s="145"/>
+      <c r="H99" s="145"/>
+      <c r="I99" s="145"/>
+      <c r="J99" s="145"/>
+      <c r="K99" s="145"/>
+      <c r="L99" s="145"/>
+      <c r="M99" s="146"/>
     </row>
     <row r="100" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="136" t="s">
+      <c r="A100" s="166" t="s">
         <v>90</v>
       </c>
-      <c r="B100" s="125"/>
-      <c r="C100" s="125"/>
-      <c r="D100" s="125"/>
-      <c r="E100" s="125"/>
-      <c r="F100" s="125"/>
-      <c r="G100" s="125"/>
-      <c r="H100" s="125"/>
-      <c r="I100" s="125"/>
-      <c r="J100" s="125"/>
-      <c r="K100" s="125"/>
-      <c r="L100" s="125"/>
-      <c r="M100" s="126"/>
+      <c r="B100" s="148"/>
+      <c r="C100" s="148"/>
+      <c r="D100" s="148"/>
+      <c r="E100" s="148"/>
+      <c r="F100" s="148"/>
+      <c r="G100" s="148"/>
+      <c r="H100" s="148"/>
+      <c r="I100" s="148"/>
+      <c r="J100" s="148"/>
+      <c r="K100" s="148"/>
+      <c r="L100" s="148"/>
+      <c r="M100" s="149"/>
     </row>
     <row r="101" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="68"/>
@@ -6164,17 +6164,17 @@
       <c r="A102" s="68"/>
       <c r="B102" s="49"/>
       <c r="C102" s="71"/>
-      <c r="D102" s="139" t="s">
+      <c r="D102" s="169" t="s">
         <v>91</v>
       </c>
-      <c r="E102" s="139"/>
-      <c r="F102" s="139"/>
-      <c r="G102" s="140" t="s">
+      <c r="E102" s="169"/>
+      <c r="F102" s="169"/>
+      <c r="G102" s="170" t="s">
         <v>92</v>
       </c>
-      <c r="H102" s="140"/>
-      <c r="I102" s="140"/>
-      <c r="J102" s="139" t="s">
+      <c r="H102" s="170"/>
+      <c r="I102" s="170"/>
+      <c r="J102" s="169" t="s">
         <v>93</v>
       </c>
       <c r="K102" s="69"/>
@@ -6185,9 +6185,9 @@
       <c r="A103" s="68"/>
       <c r="B103" s="69"/>
       <c r="C103" s="69"/>
-      <c r="D103" s="140"/>
-      <c r="E103" s="140"/>
-      <c r="F103" s="140"/>
+      <c r="D103" s="170"/>
+      <c r="E103" s="170"/>
+      <c r="F103" s="170"/>
       <c r="G103" s="65" t="s">
         <v>94</v>
       </c>
@@ -6197,7 +6197,7 @@
       <c r="I103" s="65" t="s">
         <v>96</v>
       </c>
-      <c r="J103" s="140"/>
+      <c r="J103" s="170"/>
       <c r="K103" s="69"/>
       <c r="L103" s="69"/>
       <c r="M103" s="70"/>
@@ -6206,11 +6206,11 @@
       <c r="A104" s="68"/>
       <c r="B104" s="69"/>
       <c r="C104" s="69"/>
-      <c r="D104" s="133" t="s">
+      <c r="D104" s="167" t="s">
         <v>97</v>
       </c>
-      <c r="E104" s="133"/>
-      <c r="F104" s="133"/>
+      <c r="E104" s="167"/>
+      <c r="F104" s="167"/>
       <c r="G104" s="72">
         <v>2232</v>
       </c>
@@ -6231,11 +6231,11 @@
       <c r="A105" s="68"/>
       <c r="B105" s="69"/>
       <c r="C105" s="69"/>
-      <c r="D105" s="131" t="s">
+      <c r="D105" s="168" t="s">
         <v>98</v>
       </c>
-      <c r="E105" s="131"/>
-      <c r="F105" s="131"/>
+      <c r="E105" s="168"/>
+      <c r="F105" s="168"/>
       <c r="G105" s="74">
         <v>1908</v>
       </c>
@@ -6256,11 +6256,11 @@
       <c r="A106" s="68"/>
       <c r="B106" s="69"/>
       <c r="C106" s="69"/>
-      <c r="D106" s="130" t="s">
+      <c r="D106" s="151" t="s">
         <v>99</v>
       </c>
-      <c r="E106" s="130"/>
-      <c r="F106" s="130"/>
+      <c r="E106" s="151"/>
+      <c r="F106" s="151"/>
       <c r="G106" s="17">
         <v>732</v>
       </c>
@@ -6281,11 +6281,11 @@
       <c r="A107" s="68"/>
       <c r="B107" s="69"/>
       <c r="C107" s="69"/>
-      <c r="D107" s="131" t="s">
+      <c r="D107" s="168" t="s">
         <v>100</v>
       </c>
-      <c r="E107" s="131"/>
-      <c r="F107" s="131"/>
+      <c r="E107" s="168"/>
+      <c r="F107" s="168"/>
       <c r="G107" s="18">
         <v>610</v>
       </c>
@@ -6306,11 +6306,11 @@
       <c r="A108" s="68"/>
       <c r="B108" s="69"/>
       <c r="C108" s="69"/>
-      <c r="D108" s="130" t="s">
+      <c r="D108" s="151" t="s">
         <v>101</v>
       </c>
-      <c r="E108" s="130"/>
-      <c r="F108" s="130"/>
+      <c r="E108" s="151"/>
+      <c r="F108" s="151"/>
       <c r="G108" s="17">
         <v>288</v>
       </c>
@@ -6331,11 +6331,11 @@
       <c r="A109" s="68"/>
       <c r="B109" s="69"/>
       <c r="C109" s="69"/>
-      <c r="D109" s="131" t="s">
+      <c r="D109" s="168" t="s">
         <v>102</v>
       </c>
-      <c r="E109" s="131"/>
-      <c r="F109" s="131"/>
+      <c r="E109" s="168"/>
+      <c r="F109" s="168"/>
       <c r="G109" s="18">
         <v>284</v>
       </c>
@@ -6356,11 +6356,11 @@
       <c r="A110" s="68"/>
       <c r="B110" s="69"/>
       <c r="C110" s="69"/>
-      <c r="D110" s="130" t="s">
+      <c r="D110" s="151" t="s">
         <v>103</v>
       </c>
-      <c r="E110" s="130"/>
-      <c r="F110" s="130"/>
+      <c r="E110" s="151"/>
+      <c r="F110" s="151"/>
       <c r="G110" s="17">
         <v>320</v>
       </c>
@@ -6381,11 +6381,11 @@
       <c r="A111" s="68"/>
       <c r="B111" s="69"/>
       <c r="C111" s="69"/>
-      <c r="D111" s="131" t="s">
+      <c r="D111" s="168" t="s">
         <v>104</v>
       </c>
-      <c r="E111" s="131"/>
-      <c r="F111" s="131"/>
+      <c r="E111" s="168"/>
+      <c r="F111" s="168"/>
       <c r="G111" s="18">
         <v>24</v>
       </c>
@@ -6406,11 +6406,11 @@
       <c r="A112" s="68"/>
       <c r="B112" s="69"/>
       <c r="C112" s="69"/>
-      <c r="D112" s="130" t="s">
+      <c r="D112" s="151" t="s">
         <v>105</v>
       </c>
-      <c r="E112" s="130"/>
-      <c r="F112" s="130"/>
+      <c r="E112" s="151"/>
+      <c r="F112" s="151"/>
       <c r="G112" s="17">
         <v>20</v>
       </c>
@@ -6431,11 +6431,11 @@
       <c r="A113" s="68"/>
       <c r="B113" s="69"/>
       <c r="C113" s="69"/>
-      <c r="D113" s="131" t="s">
+      <c r="D113" s="168" t="s">
         <v>106</v>
       </c>
-      <c r="E113" s="131"/>
-      <c r="F113" s="131"/>
+      <c r="E113" s="168"/>
+      <c r="F113" s="168"/>
       <c r="G113" s="18">
         <v>60</v>
       </c>
@@ -6456,11 +6456,11 @@
       <c r="A114" s="68"/>
       <c r="B114" s="69"/>
       <c r="C114" s="69"/>
-      <c r="D114" s="130" t="s">
+      <c r="D114" s="151" t="s">
         <v>107</v>
       </c>
-      <c r="E114" s="130"/>
-      <c r="F114" s="130"/>
+      <c r="E114" s="151"/>
+      <c r="F114" s="151"/>
       <c r="G114" s="17">
         <v>18</v>
       </c>
@@ -6481,11 +6481,11 @@
       <c r="A115" s="68"/>
       <c r="B115" s="69"/>
       <c r="C115" s="69"/>
-      <c r="D115" s="131" t="s">
+      <c r="D115" s="168" t="s">
         <v>108</v>
       </c>
-      <c r="E115" s="131"/>
-      <c r="F115" s="131"/>
+      <c r="E115" s="168"/>
+      <c r="F115" s="168"/>
       <c r="G115" s="18">
         <v>282</v>
       </c>
@@ -6506,11 +6506,11 @@
       <c r="A116" s="68"/>
       <c r="B116" s="69"/>
       <c r="C116" s="69"/>
-      <c r="D116" s="130" t="s">
+      <c r="D116" s="151" t="s">
         <v>109</v>
       </c>
-      <c r="E116" s="130"/>
-      <c r="F116" s="130"/>
+      <c r="E116" s="151"/>
+      <c r="F116" s="151"/>
       <c r="G116" s="17">
         <v>108</v>
       </c>
@@ -6531,11 +6531,11 @@
       <c r="A117" s="68"/>
       <c r="B117" s="69"/>
       <c r="C117" s="69"/>
-      <c r="D117" s="131" t="s">
+      <c r="D117" s="168" t="s">
         <v>110</v>
       </c>
-      <c r="E117" s="131"/>
-      <c r="F117" s="131"/>
+      <c r="E117" s="168"/>
+      <c r="F117" s="168"/>
       <c r="G117" s="18">
         <v>482</v>
       </c>
@@ -6556,11 +6556,11 @@
       <c r="A118" s="68"/>
       <c r="B118" s="69"/>
       <c r="C118" s="69"/>
-      <c r="D118" s="130" t="s">
+      <c r="D118" s="151" t="s">
         <v>111</v>
       </c>
-      <c r="E118" s="130"/>
-      <c r="F118" s="130"/>
+      <c r="E118" s="151"/>
+      <c r="F118" s="151"/>
       <c r="G118" s="17">
         <v>226</v>
       </c>
@@ -6581,11 +6581,11 @@
       <c r="A119" s="68"/>
       <c r="B119" s="69"/>
       <c r="C119" s="69"/>
-      <c r="D119" s="131" t="s">
+      <c r="D119" s="168" t="s">
         <v>112</v>
       </c>
-      <c r="E119" s="131"/>
-      <c r="F119" s="131"/>
+      <c r="E119" s="168"/>
+      <c r="F119" s="168"/>
       <c r="G119" s="18">
         <v>246</v>
       </c>
@@ -6606,11 +6606,11 @@
       <c r="A120" s="68"/>
       <c r="B120" s="69"/>
       <c r="C120" s="69"/>
-      <c r="D120" s="130" t="s">
+      <c r="D120" s="151" t="s">
         <v>113</v>
       </c>
-      <c r="E120" s="130"/>
-      <c r="F120" s="130"/>
+      <c r="E120" s="151"/>
+      <c r="F120" s="151"/>
       <c r="G120" s="17">
         <v>560</v>
       </c>
@@ -6631,11 +6631,11 @@
       <c r="A121" s="68"/>
       <c r="B121" s="69"/>
       <c r="C121" s="69"/>
-      <c r="D121" s="131" t="s">
+      <c r="D121" s="168" t="s">
         <v>114</v>
       </c>
-      <c r="E121" s="131"/>
-      <c r="F121" s="131"/>
+      <c r="E121" s="168"/>
+      <c r="F121" s="168"/>
       <c r="G121" s="18">
         <v>20</v>
       </c>
@@ -6656,11 +6656,11 @@
       <c r="A122" s="68"/>
       <c r="B122" s="69"/>
       <c r="C122" s="69"/>
-      <c r="D122" s="130" t="s">
+      <c r="D122" s="151" t="s">
         <v>115</v>
       </c>
-      <c r="E122" s="130"/>
-      <c r="F122" s="130"/>
+      <c r="E122" s="151"/>
+      <c r="F122" s="151"/>
       <c r="G122" s="17">
         <v>656</v>
       </c>
@@ -6681,11 +6681,11 @@
       <c r="A123" s="68"/>
       <c r="B123" s="69"/>
       <c r="C123" s="69"/>
-      <c r="D123" s="131" t="s">
+      <c r="D123" s="168" t="s">
         <v>116</v>
       </c>
-      <c r="E123" s="131"/>
-      <c r="F123" s="131"/>
+      <c r="E123" s="168"/>
+      <c r="F123" s="168"/>
       <c r="G123" s="74">
         <v>1416</v>
       </c>
@@ -6706,11 +6706,11 @@
       <c r="A124" s="68"/>
       <c r="B124" s="69"/>
       <c r="C124" s="69"/>
-      <c r="D124" s="130" t="s">
+      <c r="D124" s="151" t="s">
         <v>117</v>
       </c>
-      <c r="E124" s="130"/>
-      <c r="F124" s="130"/>
+      <c r="E124" s="151"/>
+      <c r="F124" s="151"/>
       <c r="G124" s="17">
         <v>554</v>
       </c>
@@ -6731,11 +6731,11 @@
       <c r="A125" s="68"/>
       <c r="B125" s="69"/>
       <c r="C125" s="69"/>
-      <c r="D125" s="131" t="s">
+      <c r="D125" s="168" t="s">
         <v>118</v>
       </c>
-      <c r="E125" s="131"/>
-      <c r="F125" s="131"/>
+      <c r="E125" s="168"/>
+      <c r="F125" s="168"/>
       <c r="G125" s="18">
         <v>196</v>
       </c>
@@ -6756,11 +6756,11 @@
       <c r="A126" s="68"/>
       <c r="B126" s="69"/>
       <c r="C126" s="69"/>
-      <c r="D126" s="130" t="s">
+      <c r="D126" s="151" t="s">
         <v>119</v>
       </c>
-      <c r="E126" s="130"/>
-      <c r="F126" s="130"/>
+      <c r="E126" s="151"/>
+      <c r="F126" s="151"/>
       <c r="G126" s="17">
         <v>292</v>
       </c>
@@ -6781,11 +6781,11 @@
       <c r="A127" s="68"/>
       <c r="B127" s="69"/>
       <c r="C127" s="69"/>
-      <c r="D127" s="131" t="s">
+      <c r="D127" s="168" t="s">
         <v>120</v>
       </c>
-      <c r="E127" s="131"/>
-      <c r="F127" s="131"/>
+      <c r="E127" s="168"/>
+      <c r="F127" s="168"/>
       <c r="G127" s="18">
         <v>180</v>
       </c>
@@ -6806,11 +6806,11 @@
       <c r="A128" s="68"/>
       <c r="B128" s="69"/>
       <c r="C128" s="69"/>
-      <c r="D128" s="130" t="s">
+      <c r="D128" s="151" t="s">
         <v>121</v>
       </c>
-      <c r="E128" s="130"/>
-      <c r="F128" s="130"/>
+      <c r="E128" s="151"/>
+      <c r="F128" s="151"/>
       <c r="G128" s="17">
         <v>294</v>
       </c>
@@ -6831,11 +6831,11 @@
       <c r="A129" s="68"/>
       <c r="B129" s="69"/>
       <c r="C129" s="69"/>
-      <c r="D129" s="131" t="s">
+      <c r="D129" s="168" t="s">
         <v>122</v>
       </c>
-      <c r="E129" s="131"/>
-      <c r="F129" s="131"/>
+      <c r="E129" s="168"/>
+      <c r="F129" s="168"/>
       <c r="G129" s="18">
         <v>744</v>
       </c>
@@ -6856,11 +6856,11 @@
       <c r="A130" s="68"/>
       <c r="B130" s="69"/>
       <c r="C130" s="69"/>
-      <c r="D130" s="130" t="s">
+      <c r="D130" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="E130" s="130"/>
-      <c r="F130" s="130"/>
+      <c r="E130" s="151"/>
+      <c r="F130" s="151"/>
       <c r="G130" s="72">
         <v>1364</v>
       </c>
@@ -6881,11 +6881,11 @@
       <c r="A131" s="68"/>
       <c r="B131" s="69"/>
       <c r="C131" s="69"/>
-      <c r="D131" s="131" t="s">
+      <c r="D131" s="168" t="s">
         <v>124</v>
       </c>
-      <c r="E131" s="131"/>
-      <c r="F131" s="131"/>
+      <c r="E131" s="168"/>
+      <c r="F131" s="168"/>
       <c r="G131" s="18">
         <v>616</v>
       </c>
@@ -6906,11 +6906,11 @@
       <c r="A132" s="68"/>
       <c r="B132" s="69"/>
       <c r="C132" s="69"/>
-      <c r="D132" s="130" t="s">
+      <c r="D132" s="151" t="s">
         <v>125</v>
       </c>
-      <c r="E132" s="130"/>
-      <c r="F132" s="130"/>
+      <c r="E132" s="151"/>
+      <c r="F132" s="151"/>
       <c r="G132" s="17">
         <v>252</v>
       </c>
@@ -6931,11 +6931,11 @@
       <c r="A133" s="68"/>
       <c r="B133" s="69"/>
       <c r="C133" s="69"/>
-      <c r="D133" s="131" t="s">
+      <c r="D133" s="168" t="s">
         <v>126</v>
       </c>
-      <c r="E133" s="131"/>
-      <c r="F133" s="131"/>
+      <c r="E133" s="168"/>
+      <c r="F133" s="168"/>
       <c r="G133" s="18">
         <v>526</v>
       </c>
@@ -6956,11 +6956,11 @@
       <c r="A134" s="68"/>
       <c r="B134" s="69"/>
       <c r="C134" s="69"/>
-      <c r="D134" s="130" t="s">
+      <c r="D134" s="151" t="s">
         <v>127</v>
       </c>
-      <c r="E134" s="130"/>
-      <c r="F134" s="130"/>
+      <c r="E134" s="151"/>
+      <c r="F134" s="151"/>
       <c r="G134" s="72">
         <v>1224</v>
       </c>
@@ -6981,11 +6981,11 @@
       <c r="A135" s="68"/>
       <c r="B135" s="69"/>
       <c r="C135" s="69"/>
-      <c r="D135" s="134" t="s">
+      <c r="D135" s="171" t="s">
         <v>128</v>
       </c>
-      <c r="E135" s="134"/>
-      <c r="F135" s="134"/>
+      <c r="E135" s="171"/>
+      <c r="F135" s="171"/>
       <c r="G135" s="77">
         <v>22</v>
       </c>
@@ -7006,11 +7006,11 @@
       <c r="A136" s="68"/>
       <c r="B136" s="69"/>
       <c r="C136" s="69"/>
-      <c r="D136" s="135" t="s">
+      <c r="D136" s="172" t="s">
         <v>129</v>
       </c>
-      <c r="E136" s="135"/>
-      <c r="F136" s="135"/>
+      <c r="E136" s="172"/>
+      <c r="F136" s="172"/>
       <c r="G136" s="79">
         <v>16756</v>
       </c>
@@ -7043,38 +7043,38 @@
       <c r="M137" s="70"/>
     </row>
     <row r="138" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="127" t="s">
+      <c r="A138" s="144" t="s">
         <v>130</v>
       </c>
-      <c r="B138" s="128"/>
-      <c r="C138" s="128"/>
-      <c r="D138" s="128"/>
-      <c r="E138" s="128"/>
-      <c r="F138" s="128"/>
-      <c r="G138" s="128"/>
-      <c r="H138" s="128"/>
-      <c r="I138" s="128"/>
-      <c r="J138" s="128"/>
-      <c r="K138" s="128"/>
-      <c r="L138" s="128"/>
-      <c r="M138" s="129"/>
+      <c r="B138" s="145"/>
+      <c r="C138" s="145"/>
+      <c r="D138" s="145"/>
+      <c r="E138" s="145"/>
+      <c r="F138" s="145"/>
+      <c r="G138" s="145"/>
+      <c r="H138" s="145"/>
+      <c r="I138" s="145"/>
+      <c r="J138" s="145"/>
+      <c r="K138" s="145"/>
+      <c r="L138" s="145"/>
+      <c r="M138" s="146"/>
     </row>
     <row r="139" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="136" t="s">
+      <c r="A139" s="166" t="s">
         <v>131</v>
       </c>
-      <c r="B139" s="125"/>
-      <c r="C139" s="125"/>
-      <c r="D139" s="125"/>
-      <c r="E139" s="125"/>
-      <c r="F139" s="125"/>
-      <c r="G139" s="125"/>
-      <c r="H139" s="125"/>
-      <c r="I139" s="125"/>
-      <c r="J139" s="125"/>
-      <c r="K139" s="125"/>
-      <c r="L139" s="125"/>
-      <c r="M139" s="126"/>
+      <c r="B139" s="148"/>
+      <c r="C139" s="148"/>
+      <c r="D139" s="148"/>
+      <c r="E139" s="148"/>
+      <c r="F139" s="148"/>
+      <c r="G139" s="148"/>
+      <c r="H139" s="148"/>
+      <c r="I139" s="148"/>
+      <c r="J139" s="148"/>
+      <c r="K139" s="148"/>
+      <c r="L139" s="148"/>
+      <c r="M139" s="149"/>
     </row>
     <row r="140" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="68"/>
@@ -7092,29 +7092,29 @@
       <c r="M140" s="70"/>
     </row>
     <row r="141" spans="1:13" s="15" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B141" s="137" t="s">
+      <c r="B141" s="173" t="s">
         <v>91</v>
       </c>
-      <c r="C141" s="137"/>
-      <c r="D141" s="137" t="s">
+      <c r="C141" s="173"/>
+      <c r="D141" s="173" t="s">
         <v>132</v>
       </c>
-      <c r="E141" s="138" t="s">
+      <c r="E141" s="174" t="s">
         <v>95</v>
       </c>
-      <c r="F141" s="138"/>
-      <c r="G141" s="138"/>
-      <c r="H141" s="138"/>
-      <c r="I141" s="138"/>
-      <c r="J141" s="138"/>
-      <c r="K141" s="138"/>
-      <c r="L141" s="138"/>
+      <c r="F141" s="174"/>
+      <c r="G141" s="174"/>
+      <c r="H141" s="174"/>
+      <c r="I141" s="174"/>
+      <c r="J141" s="174"/>
+      <c r="K141" s="174"/>
+      <c r="L141" s="174"/>
       <c r="M141" s="16"/>
     </row>
     <row r="142" spans="1:13" s="15" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B142" s="138"/>
-      <c r="C142" s="138"/>
-      <c r="D142" s="138"/>
+      <c r="B142" s="174"/>
+      <c r="C142" s="174"/>
+      <c r="D142" s="174"/>
       <c r="E142" s="66" t="s">
         <v>133</v>
       </c>
@@ -7143,10 +7143,10 @@
     </row>
     <row r="143" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="68"/>
-      <c r="B143" s="133" t="s">
+      <c r="B143" s="167" t="s">
         <v>97</v>
       </c>
-      <c r="C143" s="133"/>
+      <c r="C143" s="167"/>
       <c r="D143" s="17">
         <v>2</v>
       </c>
@@ -7178,10 +7178,10 @@
     </row>
     <row r="144" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="68"/>
-      <c r="B144" s="131" t="s">
+      <c r="B144" s="168" t="s">
         <v>98</v>
       </c>
-      <c r="C144" s="131"/>
+      <c r="C144" s="168"/>
       <c r="D144" s="18">
         <v>2</v>
       </c>
@@ -7213,10 +7213,10 @@
     </row>
     <row r="145" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="68"/>
-      <c r="B145" s="130" t="s">
+      <c r="B145" s="151" t="s">
         <v>99</v>
       </c>
-      <c r="C145" s="130"/>
+      <c r="C145" s="151"/>
       <c r="D145" s="17">
         <v>0</v>
       </c>
@@ -7248,10 +7248,10 @@
     </row>
     <row r="146" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="68"/>
-      <c r="B146" s="131" t="s">
+      <c r="B146" s="168" t="s">
         <v>100</v>
       </c>
-      <c r="C146" s="131"/>
+      <c r="C146" s="168"/>
       <c r="D146" s="18">
         <v>69</v>
       </c>
@@ -7283,10 +7283,10 @@
     </row>
     <row r="147" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="68"/>
-      <c r="B147" s="130" t="s">
+      <c r="B147" s="151" t="s">
         <v>101</v>
       </c>
-      <c r="C147" s="130"/>
+      <c r="C147" s="151"/>
       <c r="D147" s="17">
         <v>3</v>
       </c>
@@ -7318,10 +7318,10 @@
     </row>
     <row r="148" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="68"/>
-      <c r="B148" s="131" t="s">
+      <c r="B148" s="168" t="s">
         <v>102</v>
       </c>
-      <c r="C148" s="131"/>
+      <c r="C148" s="168"/>
       <c r="D148" s="18">
         <v>19</v>
       </c>
@@ -7353,10 +7353,10 @@
     </row>
     <row r="149" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="68"/>
-      <c r="B149" s="130" t="s">
+      <c r="B149" s="151" t="s">
         <v>103</v>
       </c>
-      <c r="C149" s="130"/>
+      <c r="C149" s="151"/>
       <c r="D149" s="17">
         <v>45</v>
       </c>
@@ -7388,10 +7388,10 @@
     </row>
     <row r="150" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="68"/>
-      <c r="B150" s="131" t="s">
+      <c r="B150" s="168" t="s">
         <v>104</v>
       </c>
-      <c r="C150" s="131"/>
+      <c r="C150" s="168"/>
       <c r="D150" s="18">
         <v>2</v>
       </c>
@@ -7423,10 +7423,10 @@
     </row>
     <row r="151" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="68"/>
-      <c r="B151" s="130" t="s">
+      <c r="B151" s="151" t="s">
         <v>105</v>
       </c>
-      <c r="C151" s="130"/>
+      <c r="C151" s="151"/>
       <c r="D151" s="17">
         <v>1</v>
       </c>
@@ -7458,10 +7458,10 @@
     </row>
     <row r="152" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="68"/>
-      <c r="B152" s="131" t="s">
+      <c r="B152" s="168" t="s">
         <v>106</v>
       </c>
-      <c r="C152" s="131"/>
+      <c r="C152" s="168"/>
       <c r="D152" s="18">
         <v>0</v>
       </c>
@@ -7493,10 +7493,10 @@
     </row>
     <row r="153" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="68"/>
-      <c r="B153" s="130" t="s">
+      <c r="B153" s="151" t="s">
         <v>107</v>
       </c>
-      <c r="C153" s="130"/>
+      <c r="C153" s="151"/>
       <c r="D153" s="17">
         <v>4</v>
       </c>
@@ -7528,10 +7528,10 @@
     </row>
     <row r="154" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="68"/>
-      <c r="B154" s="131" t="s">
+      <c r="B154" s="168" t="s">
         <v>108</v>
       </c>
-      <c r="C154" s="131"/>
+      <c r="C154" s="168"/>
       <c r="D154" s="18">
         <v>4</v>
       </c>
@@ -7563,10 +7563,10 @@
     </row>
     <row r="155" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="68"/>
-      <c r="B155" s="130" t="s">
+      <c r="B155" s="151" t="s">
         <v>109</v>
       </c>
-      <c r="C155" s="130"/>
+      <c r="C155" s="151"/>
       <c r="D155" s="17">
         <v>0</v>
       </c>
@@ -7598,10 +7598,10 @@
     </row>
     <row r="156" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="68"/>
-      <c r="B156" s="131" t="s">
+      <c r="B156" s="168" t="s">
         <v>110</v>
       </c>
-      <c r="C156" s="131"/>
+      <c r="C156" s="168"/>
       <c r="D156" s="18">
         <v>0</v>
       </c>
@@ -7633,10 +7633,10 @@
     </row>
     <row r="157" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="68"/>
-      <c r="B157" s="130" t="s">
+      <c r="B157" s="151" t="s">
         <v>111</v>
       </c>
-      <c r="C157" s="130"/>
+      <c r="C157" s="151"/>
       <c r="D157" s="17">
         <v>8</v>
       </c>
@@ -7668,10 +7668,10 @@
     </row>
     <row r="158" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="68"/>
-      <c r="B158" s="131" t="s">
+      <c r="B158" s="168" t="s">
         <v>112</v>
       </c>
-      <c r="C158" s="131"/>
+      <c r="C158" s="168"/>
       <c r="D158" s="18">
         <v>4</v>
       </c>
@@ -7703,10 +7703,10 @@
     </row>
     <row r="159" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="68"/>
-      <c r="B159" s="130" t="s">
+      <c r="B159" s="151" t="s">
         <v>113</v>
       </c>
-      <c r="C159" s="130"/>
+      <c r="C159" s="151"/>
       <c r="D159" s="17">
         <v>0</v>
       </c>
@@ -7738,10 +7738,10 @@
     </row>
     <row r="160" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="68"/>
-      <c r="B160" s="131" t="s">
+      <c r="B160" s="168" t="s">
         <v>114</v>
       </c>
-      <c r="C160" s="131"/>
+      <c r="C160" s="168"/>
       <c r="D160" s="18">
         <v>0</v>
       </c>
@@ -7773,10 +7773,10 @@
     </row>
     <row r="161" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="68"/>
-      <c r="B161" s="130" t="s">
+      <c r="B161" s="151" t="s">
         <v>115</v>
       </c>
-      <c r="C161" s="130"/>
+      <c r="C161" s="151"/>
       <c r="D161" s="17">
         <v>35</v>
       </c>
@@ -7808,10 +7808,10 @@
     </row>
     <row r="162" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="68"/>
-      <c r="B162" s="131" t="s">
+      <c r="B162" s="168" t="s">
         <v>116</v>
       </c>
-      <c r="C162" s="131"/>
+      <c r="C162" s="168"/>
       <c r="D162" s="18">
         <v>55</v>
       </c>
@@ -7843,10 +7843,10 @@
     </row>
     <row r="163" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="68"/>
-      <c r="B163" s="130" t="s">
+      <c r="B163" s="151" t="s">
         <v>117</v>
       </c>
-      <c r="C163" s="130"/>
+      <c r="C163" s="151"/>
       <c r="D163" s="17">
         <v>19</v>
       </c>
@@ -7878,10 +7878,10 @@
     </row>
     <row r="164" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="68"/>
-      <c r="B164" s="131" t="s">
+      <c r="B164" s="168" t="s">
         <v>118</v>
       </c>
-      <c r="C164" s="131"/>
+      <c r="C164" s="168"/>
       <c r="D164" s="18">
         <v>7</v>
       </c>
@@ -7913,10 +7913,10 @@
     </row>
     <row r="165" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="68"/>
-      <c r="B165" s="130" t="s">
+      <c r="B165" s="151" t="s">
         <v>119</v>
       </c>
-      <c r="C165" s="130"/>
+      <c r="C165" s="151"/>
       <c r="D165" s="17">
         <v>2</v>
       </c>
@@ -7948,10 +7948,10 @@
     </row>
     <row r="166" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="68"/>
-      <c r="B166" s="131" t="s">
+      <c r="B166" s="168" t="s">
         <v>120</v>
       </c>
-      <c r="C166" s="131"/>
+      <c r="C166" s="168"/>
       <c r="D166" s="18">
         <v>0</v>
       </c>
@@ -7983,10 +7983,10 @@
     </row>
     <row r="167" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="68"/>
-      <c r="B167" s="130" t="s">
+      <c r="B167" s="151" t="s">
         <v>121</v>
       </c>
-      <c r="C167" s="130"/>
+      <c r="C167" s="151"/>
       <c r="D167" s="17">
         <v>1</v>
       </c>
@@ -8018,10 +8018,10 @@
     </row>
     <row r="168" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="68"/>
-      <c r="B168" s="131" t="s">
+      <c r="B168" s="168" t="s">
         <v>122</v>
       </c>
-      <c r="C168" s="131"/>
+      <c r="C168" s="168"/>
       <c r="D168" s="18">
         <v>0</v>
       </c>
@@ -8053,10 +8053,10 @@
     </row>
     <row r="169" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="68"/>
-      <c r="B169" s="130" t="s">
+      <c r="B169" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="C169" s="130"/>
+      <c r="C169" s="151"/>
       <c r="D169" s="17">
         <v>46</v>
       </c>
@@ -8088,10 +8088,10 @@
     </row>
     <row r="170" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="68"/>
-      <c r="B170" s="131" t="s">
+      <c r="B170" s="168" t="s">
         <v>124</v>
       </c>
-      <c r="C170" s="131"/>
+      <c r="C170" s="168"/>
       <c r="D170" s="18">
         <v>14</v>
       </c>
@@ -8123,10 +8123,10 @@
     </row>
     <row r="171" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="68"/>
-      <c r="B171" s="130" t="s">
+      <c r="B171" s="151" t="s">
         <v>125</v>
       </c>
-      <c r="C171" s="130"/>
+      <c r="C171" s="151"/>
       <c r="D171" s="17">
         <v>0</v>
       </c>
@@ -8158,10 +8158,10 @@
     </row>
     <row r="172" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="68"/>
-      <c r="B172" s="131" t="s">
+      <c r="B172" s="168" t="s">
         <v>126</v>
       </c>
-      <c r="C172" s="131"/>
+      <c r="C172" s="168"/>
       <c r="D172" s="18">
         <v>93</v>
       </c>
@@ -8193,10 +8193,10 @@
     </row>
     <row r="173" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="68"/>
-      <c r="B173" s="130" t="s">
+      <c r="B173" s="151" t="s">
         <v>127</v>
       </c>
-      <c r="C173" s="130"/>
+      <c r="C173" s="151"/>
       <c r="D173" s="17">
         <v>25</v>
       </c>
@@ -8228,10 +8228,10 @@
     </row>
     <row r="174" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="68"/>
-      <c r="B174" s="131" t="s">
+      <c r="B174" s="168" t="s">
         <v>128</v>
       </c>
-      <c r="C174" s="131"/>
+      <c r="C174" s="168"/>
       <c r="D174" s="18">
         <v>4</v>
       </c>
@@ -8263,10 +8263,10 @@
     </row>
     <row r="175" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="68"/>
-      <c r="B175" s="132" t="s">
+      <c r="B175" s="178" t="s">
         <v>129</v>
       </c>
-      <c r="C175" s="132"/>
+      <c r="C175" s="178"/>
       <c r="D175" s="19">
         <v>464</v>
       </c>
@@ -8312,174 +8312,174 @@
       <c r="M176" s="70"/>
     </row>
     <row r="177" spans="1:13" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="127" t="s">
+      <c r="A177" s="144" t="s">
         <v>141</v>
       </c>
-      <c r="B177" s="128"/>
-      <c r="C177" s="128"/>
-      <c r="D177" s="128"/>
-      <c r="E177" s="128"/>
-      <c r="F177" s="128"/>
-      <c r="G177" s="128"/>
-      <c r="H177" s="128"/>
-      <c r="I177" s="128"/>
-      <c r="J177" s="128"/>
-      <c r="K177" s="128"/>
-      <c r="L177" s="128"/>
-      <c r="M177" s="129"/>
+      <c r="B177" s="145"/>
+      <c r="C177" s="145"/>
+      <c r="D177" s="145"/>
+      <c r="E177" s="145"/>
+      <c r="F177" s="145"/>
+      <c r="G177" s="145"/>
+      <c r="H177" s="145"/>
+      <c r="I177" s="145"/>
+      <c r="J177" s="145"/>
+      <c r="K177" s="145"/>
+      <c r="L177" s="145"/>
+      <c r="M177" s="146"/>
     </row>
     <row r="178" spans="1:13" s="14" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="124" t="s">
+      <c r="A178" s="147" t="s">
         <v>142</v>
       </c>
-      <c r="B178" s="125"/>
-      <c r="C178" s="125"/>
-      <c r="D178" s="125"/>
-      <c r="E178" s="125"/>
-      <c r="F178" s="125"/>
-      <c r="G178" s="125"/>
-      <c r="H178" s="125"/>
-      <c r="I178" s="125"/>
-      <c r="J178" s="125"/>
-      <c r="K178" s="125"/>
-      <c r="L178" s="125"/>
-      <c r="M178" s="126"/>
+      <c r="B178" s="148"/>
+      <c r="C178" s="148"/>
+      <c r="D178" s="148"/>
+      <c r="E178" s="148"/>
+      <c r="F178" s="148"/>
+      <c r="G178" s="148"/>
+      <c r="H178" s="148"/>
+      <c r="I178" s="148"/>
+      <c r="J178" s="148"/>
+      <c r="K178" s="148"/>
+      <c r="L178" s="148"/>
+      <c r="M178" s="149"/>
     </row>
     <row r="179" spans="1:13" s="14" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="124" t="s">
+      <c r="A179" s="147" t="s">
         <v>143</v>
       </c>
-      <c r="B179" s="125"/>
-      <c r="C179" s="125"/>
-      <c r="D179" s="125"/>
-      <c r="E179" s="125"/>
-      <c r="F179" s="125"/>
-      <c r="G179" s="125"/>
-      <c r="H179" s="125"/>
-      <c r="I179" s="125"/>
-      <c r="J179" s="125"/>
-      <c r="K179" s="125"/>
-      <c r="L179" s="125"/>
-      <c r="M179" s="126"/>
+      <c r="B179" s="148"/>
+      <c r="C179" s="148"/>
+      <c r="D179" s="148"/>
+      <c r="E179" s="148"/>
+      <c r="F179" s="148"/>
+      <c r="G179" s="148"/>
+      <c r="H179" s="148"/>
+      <c r="I179" s="148"/>
+      <c r="J179" s="148"/>
+      <c r="K179" s="148"/>
+      <c r="L179" s="148"/>
+      <c r="M179" s="149"/>
     </row>
     <row r="180" spans="1:13" s="14" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="124" t="s">
+      <c r="A180" s="147" t="s">
         <v>144</v>
       </c>
-      <c r="B180" s="125"/>
-      <c r="C180" s="125"/>
-      <c r="D180" s="125"/>
-      <c r="E180" s="125"/>
-      <c r="F180" s="125"/>
-      <c r="G180" s="125"/>
-      <c r="H180" s="125"/>
-      <c r="I180" s="125"/>
-      <c r="J180" s="125"/>
-      <c r="K180" s="125"/>
-      <c r="L180" s="125"/>
-      <c r="M180" s="126"/>
+      <c r="B180" s="148"/>
+      <c r="C180" s="148"/>
+      <c r="D180" s="148"/>
+      <c r="E180" s="148"/>
+      <c r="F180" s="148"/>
+      <c r="G180" s="148"/>
+      <c r="H180" s="148"/>
+      <c r="I180" s="148"/>
+      <c r="J180" s="148"/>
+      <c r="K180" s="148"/>
+      <c r="L180" s="148"/>
+      <c r="M180" s="149"/>
     </row>
     <row r="181" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="127" t="s">
+      <c r="A181" s="144" t="s">
         <v>145</v>
       </c>
-      <c r="B181" s="128"/>
-      <c r="C181" s="128"/>
-      <c r="D181" s="128"/>
-      <c r="E181" s="128"/>
-      <c r="F181" s="128"/>
-      <c r="G181" s="128"/>
-      <c r="H181" s="128"/>
-      <c r="I181" s="128"/>
-      <c r="J181" s="128"/>
-      <c r="K181" s="128"/>
-      <c r="L181" s="128"/>
-      <c r="M181" s="129"/>
+      <c r="B181" s="145"/>
+      <c r="C181" s="145"/>
+      <c r="D181" s="145"/>
+      <c r="E181" s="145"/>
+      <c r="F181" s="145"/>
+      <c r="G181" s="145"/>
+      <c r="H181" s="145"/>
+      <c r="I181" s="145"/>
+      <c r="J181" s="145"/>
+      <c r="K181" s="145"/>
+      <c r="L181" s="145"/>
+      <c r="M181" s="146"/>
     </row>
     <row r="182" spans="1:13" s="14" customFormat="1" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="124" t="s">
+      <c r="A182" s="147" t="s">
         <v>146</v>
       </c>
-      <c r="B182" s="125"/>
-      <c r="C182" s="125"/>
-      <c r="D182" s="125"/>
-      <c r="E182" s="125"/>
-      <c r="F182" s="125"/>
-      <c r="G182" s="125"/>
-      <c r="H182" s="125"/>
-      <c r="I182" s="125"/>
-      <c r="J182" s="125"/>
-      <c r="K182" s="125"/>
-      <c r="L182" s="125"/>
-      <c r="M182" s="126"/>
+      <c r="B182" s="148"/>
+      <c r="C182" s="148"/>
+      <c r="D182" s="148"/>
+      <c r="E182" s="148"/>
+      <c r="F182" s="148"/>
+      <c r="G182" s="148"/>
+      <c r="H182" s="148"/>
+      <c r="I182" s="148"/>
+      <c r="J182" s="148"/>
+      <c r="K182" s="148"/>
+      <c r="L182" s="148"/>
+      <c r="M182" s="149"/>
     </row>
     <row r="183" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="127" t="s">
+      <c r="A183" s="144" t="s">
         <v>147</v>
       </c>
-      <c r="B183" s="128"/>
-      <c r="C183" s="128"/>
-      <c r="D183" s="128"/>
-      <c r="E183" s="128"/>
-      <c r="F183" s="128"/>
-      <c r="G183" s="128"/>
-      <c r="H183" s="128"/>
-      <c r="I183" s="128"/>
-      <c r="J183" s="128"/>
-      <c r="K183" s="128"/>
-      <c r="L183" s="128"/>
-      <c r="M183" s="129"/>
+      <c r="B183" s="145"/>
+      <c r="C183" s="145"/>
+      <c r="D183" s="145"/>
+      <c r="E183" s="145"/>
+      <c r="F183" s="145"/>
+      <c r="G183" s="145"/>
+      <c r="H183" s="145"/>
+      <c r="I183" s="145"/>
+      <c r="J183" s="145"/>
+      <c r="K183" s="145"/>
+      <c r="L183" s="145"/>
+      <c r="M183" s="146"/>
     </row>
     <row r="184" spans="1:13" s="14" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="124" t="s">
+      <c r="A184" s="147" t="s">
         <v>148</v>
       </c>
-      <c r="B184" s="125"/>
-      <c r="C184" s="125"/>
-      <c r="D184" s="125"/>
-      <c r="E184" s="125"/>
-      <c r="F184" s="125"/>
-      <c r="G184" s="125"/>
-      <c r="H184" s="125"/>
-      <c r="I184" s="125"/>
-      <c r="J184" s="125"/>
-      <c r="K184" s="125"/>
-      <c r="L184" s="125"/>
-      <c r="M184" s="126"/>
+      <c r="B184" s="148"/>
+      <c r="C184" s="148"/>
+      <c r="D184" s="148"/>
+      <c r="E184" s="148"/>
+      <c r="F184" s="148"/>
+      <c r="G184" s="148"/>
+      <c r="H184" s="148"/>
+      <c r="I184" s="148"/>
+      <c r="J184" s="148"/>
+      <c r="K184" s="148"/>
+      <c r="L184" s="148"/>
+      <c r="M184" s="149"/>
     </row>
     <row r="185" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="127" t="s">
+      <c r="A185" s="144" t="s">
         <v>149</v>
       </c>
-      <c r="B185" s="128"/>
-      <c r="C185" s="128"/>
-      <c r="D185" s="128"/>
-      <c r="E185" s="128"/>
-      <c r="F185" s="128"/>
-      <c r="G185" s="128"/>
-      <c r="H185" s="128"/>
-      <c r="I185" s="128"/>
-      <c r="J185" s="128"/>
-      <c r="K185" s="128"/>
-      <c r="L185" s="128"/>
-      <c r="M185" s="129"/>
+      <c r="B185" s="145"/>
+      <c r="C185" s="145"/>
+      <c r="D185" s="145"/>
+      <c r="E185" s="145"/>
+      <c r="F185" s="145"/>
+      <c r="G185" s="145"/>
+      <c r="H185" s="145"/>
+      <c r="I185" s="145"/>
+      <c r="J185" s="145"/>
+      <c r="K185" s="145"/>
+      <c r="L185" s="145"/>
+      <c r="M185" s="146"/>
     </row>
     <row r="186" spans="1:13" s="14" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="121" t="s">
+      <c r="A186" s="175" t="s">
         <v>150</v>
       </c>
-      <c r="B186" s="122"/>
-      <c r="C186" s="122"/>
-      <c r="D186" s="122"/>
-      <c r="E186" s="122"/>
-      <c r="F186" s="122"/>
-      <c r="G186" s="122"/>
-      <c r="H186" s="122"/>
-      <c r="I186" s="122"/>
-      <c r="J186" s="122"/>
-      <c r="K186" s="122"/>
-      <c r="L186" s="122"/>
-      <c r="M186" s="123"/>
+      <c r="B186" s="176"/>
+      <c r="C186" s="176"/>
+      <c r="D186" s="176"/>
+      <c r="E186" s="176"/>
+      <c r="F186" s="176"/>
+      <c r="G186" s="176"/>
+      <c r="H186" s="176"/>
+      <c r="I186" s="176"/>
+      <c r="J186" s="176"/>
+      <c r="K186" s="176"/>
+      <c r="L186" s="176"/>
+      <c r="M186" s="177"/>
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A187" s="20" t="s">
@@ -8496,90 +8496,81 @@
     </row>
   </sheetData>
   <mergeCells count="173">
-    <mergeCell ref="A9:M9"/>
-    <mergeCell ref="A10:M10"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A12:M20"/>
-    <mergeCell ref="A21:M21"/>
-    <mergeCell ref="A22:M23"/>
-    <mergeCell ref="A1:M2"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="A4:M5"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="A30:M30"/>
-    <mergeCell ref="A31:M31"/>
-    <mergeCell ref="A32:M32"/>
-    <mergeCell ref="A33:M33"/>
-    <mergeCell ref="A34:M34"/>
-    <mergeCell ref="A35:M35"/>
-    <mergeCell ref="A24:M24"/>
-    <mergeCell ref="A25:M25"/>
-    <mergeCell ref="A26:M26"/>
-    <mergeCell ref="A27:M27"/>
-    <mergeCell ref="A28:M28"/>
-    <mergeCell ref="A29:M29"/>
-    <mergeCell ref="A42:M42"/>
-    <mergeCell ref="A43:M43"/>
-    <mergeCell ref="A44:M44"/>
-    <mergeCell ref="A45:M45"/>
-    <mergeCell ref="A46:M46"/>
-    <mergeCell ref="A47:M47"/>
-    <mergeCell ref="A36:M36"/>
-    <mergeCell ref="A37:M37"/>
-    <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A39:M39"/>
-    <mergeCell ref="A40:M40"/>
-    <mergeCell ref="A41:M41"/>
-    <mergeCell ref="A54:M54"/>
-    <mergeCell ref="A55:M55"/>
-    <mergeCell ref="A56:M56"/>
-    <mergeCell ref="A57:M57"/>
-    <mergeCell ref="A58:M58"/>
-    <mergeCell ref="A59:M59"/>
-    <mergeCell ref="A48:M48"/>
-    <mergeCell ref="A49:M49"/>
-    <mergeCell ref="A50:M50"/>
-    <mergeCell ref="A51:M51"/>
-    <mergeCell ref="A52:M52"/>
-    <mergeCell ref="A53:M53"/>
-    <mergeCell ref="A66:M66"/>
-    <mergeCell ref="A67:M67"/>
-    <mergeCell ref="A68:M68"/>
-    <mergeCell ref="A69:M69"/>
-    <mergeCell ref="A70:M70"/>
-    <mergeCell ref="A71:M71"/>
-    <mergeCell ref="A60:M60"/>
-    <mergeCell ref="A61:M61"/>
-    <mergeCell ref="A62:M62"/>
-    <mergeCell ref="A63:M63"/>
-    <mergeCell ref="A64:M64"/>
-    <mergeCell ref="A65:M65"/>
-    <mergeCell ref="A78:M78"/>
-    <mergeCell ref="A79:M79"/>
-    <mergeCell ref="A80:M80"/>
-    <mergeCell ref="A81:M81"/>
-    <mergeCell ref="A82:M82"/>
-    <mergeCell ref="A83:M83"/>
-    <mergeCell ref="A72:M72"/>
-    <mergeCell ref="A73:M73"/>
-    <mergeCell ref="A74:M74"/>
-    <mergeCell ref="A75:M75"/>
-    <mergeCell ref="A76:M76"/>
-    <mergeCell ref="A77:M77"/>
-    <mergeCell ref="A90:M90"/>
-    <mergeCell ref="A91:M91"/>
-    <mergeCell ref="A92:M92"/>
-    <mergeCell ref="A93:M93"/>
-    <mergeCell ref="A94:M94"/>
-    <mergeCell ref="A95:M95"/>
-    <mergeCell ref="A84:M84"/>
-    <mergeCell ref="A85:M85"/>
-    <mergeCell ref="A86:M86"/>
-    <mergeCell ref="A87:M87"/>
-    <mergeCell ref="A88:M88"/>
-    <mergeCell ref="A89:M89"/>
+    <mergeCell ref="A186:M186"/>
+    <mergeCell ref="A180:M180"/>
+    <mergeCell ref="A181:M181"/>
+    <mergeCell ref="A182:M182"/>
+    <mergeCell ref="A183:M183"/>
+    <mergeCell ref="A184:M184"/>
+    <mergeCell ref="A185:M185"/>
+    <mergeCell ref="B173:C173"/>
+    <mergeCell ref="B174:C174"/>
+    <mergeCell ref="B175:C175"/>
+    <mergeCell ref="A177:M177"/>
+    <mergeCell ref="A178:M178"/>
+    <mergeCell ref="A179:M179"/>
+    <mergeCell ref="B167:C167"/>
+    <mergeCell ref="B168:C168"/>
+    <mergeCell ref="B169:C169"/>
+    <mergeCell ref="B170:C170"/>
+    <mergeCell ref="B171:C171"/>
+    <mergeCell ref="B172:C172"/>
+    <mergeCell ref="B161:C161"/>
+    <mergeCell ref="B162:C162"/>
+    <mergeCell ref="B163:C163"/>
+    <mergeCell ref="B164:C164"/>
+    <mergeCell ref="B165:C165"/>
+    <mergeCell ref="B166:C166"/>
+    <mergeCell ref="B155:C155"/>
+    <mergeCell ref="B156:C156"/>
+    <mergeCell ref="B157:C157"/>
+    <mergeCell ref="B158:C158"/>
+    <mergeCell ref="B159:C159"/>
+    <mergeCell ref="B160:C160"/>
+    <mergeCell ref="B149:C149"/>
+    <mergeCell ref="B150:C150"/>
+    <mergeCell ref="B151:C151"/>
+    <mergeCell ref="B152:C152"/>
+    <mergeCell ref="B153:C153"/>
+    <mergeCell ref="B154:C154"/>
+    <mergeCell ref="B143:C143"/>
+    <mergeCell ref="B144:C144"/>
+    <mergeCell ref="B145:C145"/>
+    <mergeCell ref="B146:C146"/>
+    <mergeCell ref="B147:C147"/>
+    <mergeCell ref="B148:C148"/>
+    <mergeCell ref="D134:F134"/>
+    <mergeCell ref="D135:F135"/>
+    <mergeCell ref="D136:F136"/>
+    <mergeCell ref="A138:M138"/>
+    <mergeCell ref="A139:M139"/>
+    <mergeCell ref="B141:C142"/>
+    <mergeCell ref="D141:D142"/>
+    <mergeCell ref="E141:L141"/>
+    <mergeCell ref="D128:F128"/>
+    <mergeCell ref="D129:F129"/>
+    <mergeCell ref="D130:F130"/>
+    <mergeCell ref="D131:F131"/>
+    <mergeCell ref="D132:F132"/>
+    <mergeCell ref="D133:F133"/>
+    <mergeCell ref="D122:F122"/>
+    <mergeCell ref="D123:F123"/>
+    <mergeCell ref="D124:F124"/>
+    <mergeCell ref="D125:F125"/>
+    <mergeCell ref="D126:F126"/>
+    <mergeCell ref="D127:F127"/>
+    <mergeCell ref="D116:F116"/>
+    <mergeCell ref="D117:F117"/>
+    <mergeCell ref="D118:F118"/>
+    <mergeCell ref="D119:F119"/>
+    <mergeCell ref="D120:F120"/>
+    <mergeCell ref="D121:F121"/>
+    <mergeCell ref="D110:F110"/>
+    <mergeCell ref="D111:F111"/>
+    <mergeCell ref="D112:F112"/>
+    <mergeCell ref="D113:F113"/>
+    <mergeCell ref="D114:F114"/>
+    <mergeCell ref="D115:F115"/>
     <mergeCell ref="D104:F104"/>
     <mergeCell ref="D105:F105"/>
     <mergeCell ref="D106:F106"/>
@@ -8594,81 +8585,90 @@
     <mergeCell ref="D102:F103"/>
     <mergeCell ref="G102:I102"/>
     <mergeCell ref="J102:J103"/>
-    <mergeCell ref="D116:F116"/>
-    <mergeCell ref="D117:F117"/>
-    <mergeCell ref="D118:F118"/>
-    <mergeCell ref="D119:F119"/>
-    <mergeCell ref="D120:F120"/>
-    <mergeCell ref="D121:F121"/>
-    <mergeCell ref="D110:F110"/>
-    <mergeCell ref="D111:F111"/>
-    <mergeCell ref="D112:F112"/>
-    <mergeCell ref="D113:F113"/>
-    <mergeCell ref="D114:F114"/>
-    <mergeCell ref="D115:F115"/>
-    <mergeCell ref="D128:F128"/>
-    <mergeCell ref="D129:F129"/>
-    <mergeCell ref="D130:F130"/>
-    <mergeCell ref="D131:F131"/>
-    <mergeCell ref="D132:F132"/>
-    <mergeCell ref="D133:F133"/>
-    <mergeCell ref="D122:F122"/>
-    <mergeCell ref="D123:F123"/>
-    <mergeCell ref="D124:F124"/>
-    <mergeCell ref="D125:F125"/>
-    <mergeCell ref="D126:F126"/>
-    <mergeCell ref="D127:F127"/>
-    <mergeCell ref="B143:C143"/>
-    <mergeCell ref="B144:C144"/>
-    <mergeCell ref="B145:C145"/>
-    <mergeCell ref="B146:C146"/>
-    <mergeCell ref="B147:C147"/>
-    <mergeCell ref="B148:C148"/>
-    <mergeCell ref="D134:F134"/>
-    <mergeCell ref="D135:F135"/>
-    <mergeCell ref="D136:F136"/>
-    <mergeCell ref="A138:M138"/>
-    <mergeCell ref="A139:M139"/>
-    <mergeCell ref="B141:C142"/>
-    <mergeCell ref="D141:D142"/>
-    <mergeCell ref="E141:L141"/>
-    <mergeCell ref="B155:C155"/>
-    <mergeCell ref="B156:C156"/>
-    <mergeCell ref="B157:C157"/>
-    <mergeCell ref="B158:C158"/>
-    <mergeCell ref="B159:C159"/>
-    <mergeCell ref="B160:C160"/>
-    <mergeCell ref="B149:C149"/>
-    <mergeCell ref="B150:C150"/>
-    <mergeCell ref="B151:C151"/>
-    <mergeCell ref="B152:C152"/>
-    <mergeCell ref="B153:C153"/>
-    <mergeCell ref="B154:C154"/>
-    <mergeCell ref="B167:C167"/>
-    <mergeCell ref="B168:C168"/>
-    <mergeCell ref="B169:C169"/>
-    <mergeCell ref="B170:C170"/>
-    <mergeCell ref="B171:C171"/>
-    <mergeCell ref="B172:C172"/>
-    <mergeCell ref="B161:C161"/>
-    <mergeCell ref="B162:C162"/>
-    <mergeCell ref="B163:C163"/>
-    <mergeCell ref="B164:C164"/>
-    <mergeCell ref="B165:C165"/>
-    <mergeCell ref="B166:C166"/>
-    <mergeCell ref="A186:M186"/>
-    <mergeCell ref="A180:M180"/>
-    <mergeCell ref="A181:M181"/>
-    <mergeCell ref="A182:M182"/>
-    <mergeCell ref="A183:M183"/>
-    <mergeCell ref="A184:M184"/>
-    <mergeCell ref="A185:M185"/>
-    <mergeCell ref="B173:C173"/>
-    <mergeCell ref="B174:C174"/>
-    <mergeCell ref="B175:C175"/>
-    <mergeCell ref="A177:M177"/>
-    <mergeCell ref="A178:M178"/>
-    <mergeCell ref="A179:M179"/>
+    <mergeCell ref="A90:M90"/>
+    <mergeCell ref="A91:M91"/>
+    <mergeCell ref="A92:M92"/>
+    <mergeCell ref="A93:M93"/>
+    <mergeCell ref="A94:M94"/>
+    <mergeCell ref="A95:M95"/>
+    <mergeCell ref="A84:M84"/>
+    <mergeCell ref="A85:M85"/>
+    <mergeCell ref="A86:M86"/>
+    <mergeCell ref="A87:M87"/>
+    <mergeCell ref="A88:M88"/>
+    <mergeCell ref="A89:M89"/>
+    <mergeCell ref="A78:M78"/>
+    <mergeCell ref="A79:M79"/>
+    <mergeCell ref="A80:M80"/>
+    <mergeCell ref="A81:M81"/>
+    <mergeCell ref="A82:M82"/>
+    <mergeCell ref="A83:M83"/>
+    <mergeCell ref="A72:M72"/>
+    <mergeCell ref="A73:M73"/>
+    <mergeCell ref="A74:M74"/>
+    <mergeCell ref="A75:M75"/>
+    <mergeCell ref="A76:M76"/>
+    <mergeCell ref="A77:M77"/>
+    <mergeCell ref="A66:M66"/>
+    <mergeCell ref="A67:M67"/>
+    <mergeCell ref="A68:M68"/>
+    <mergeCell ref="A69:M69"/>
+    <mergeCell ref="A70:M70"/>
+    <mergeCell ref="A71:M71"/>
+    <mergeCell ref="A60:M60"/>
+    <mergeCell ref="A61:M61"/>
+    <mergeCell ref="A62:M62"/>
+    <mergeCell ref="A63:M63"/>
+    <mergeCell ref="A64:M64"/>
+    <mergeCell ref="A65:M65"/>
+    <mergeCell ref="A54:M54"/>
+    <mergeCell ref="A55:M55"/>
+    <mergeCell ref="A56:M56"/>
+    <mergeCell ref="A57:M57"/>
+    <mergeCell ref="A58:M58"/>
+    <mergeCell ref="A59:M59"/>
+    <mergeCell ref="A48:M48"/>
+    <mergeCell ref="A49:M49"/>
+    <mergeCell ref="A50:M50"/>
+    <mergeCell ref="A51:M51"/>
+    <mergeCell ref="A52:M52"/>
+    <mergeCell ref="A53:M53"/>
+    <mergeCell ref="A42:M42"/>
+    <mergeCell ref="A43:M43"/>
+    <mergeCell ref="A44:M44"/>
+    <mergeCell ref="A45:M45"/>
+    <mergeCell ref="A46:M46"/>
+    <mergeCell ref="A47:M47"/>
+    <mergeCell ref="A36:M36"/>
+    <mergeCell ref="A37:M37"/>
+    <mergeCell ref="A38:M38"/>
+    <mergeCell ref="A39:M39"/>
+    <mergeCell ref="A40:M40"/>
+    <mergeCell ref="A41:M41"/>
+    <mergeCell ref="A30:M30"/>
+    <mergeCell ref="A31:M31"/>
+    <mergeCell ref="A32:M32"/>
+    <mergeCell ref="A33:M33"/>
+    <mergeCell ref="A34:M34"/>
+    <mergeCell ref="A35:M35"/>
+    <mergeCell ref="A24:M24"/>
+    <mergeCell ref="A25:M25"/>
+    <mergeCell ref="A26:M26"/>
+    <mergeCell ref="A27:M27"/>
+    <mergeCell ref="A28:M28"/>
+    <mergeCell ref="A29:M29"/>
+    <mergeCell ref="A9:M9"/>
+    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A12:M20"/>
+    <mergeCell ref="A21:M21"/>
+    <mergeCell ref="A22:M23"/>
+    <mergeCell ref="A1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="A4:M5"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="A8:M8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="N1" location="Índice!A1" display="Regresar al índice" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
@@ -8691,69 +8691,69 @@
   <sheetData>
     <row r="1" spans="1:27" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="23"/>
-      <c r="Z1" s="147" t="s">
+      <c r="Z1" s="106" t="s">
         <v>4</v>
       </c>
-      <c r="AA1" s="147"/>
+      <c r="AA1" s="106"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="26"/>
     </row>
     <row r="3" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="107" t="s">
         <v>152</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="158"/>
-      <c r="D3" s="158"/>
-      <c r="E3" s="158"/>
-      <c r="F3" s="158"/>
-      <c r="G3" s="158"/>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="158"/>
-      <c r="K3" s="158"/>
-      <c r="L3" s="158"/>
-      <c r="M3" s="158"/>
-      <c r="N3" s="158"/>
-      <c r="O3" s="158"/>
-      <c r="P3" s="158"/>
-      <c r="Q3" s="158"/>
-      <c r="R3" s="158"/>
-      <c r="S3" s="158"/>
-      <c r="T3" s="158"/>
-      <c r="U3" s="158"/>
-      <c r="V3" s="158"/>
-      <c r="W3" s="158"/>
-      <c r="X3" s="158"/>
-      <c r="Y3" s="159"/>
+      <c r="B3" s="108"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="108"/>
+      <c r="H3" s="108"/>
+      <c r="I3" s="108"/>
+      <c r="J3" s="108"/>
+      <c r="K3" s="108"/>
+      <c r="L3" s="108"/>
+      <c r="M3" s="108"/>
+      <c r="N3" s="108"/>
+      <c r="O3" s="108"/>
+      <c r="P3" s="108"/>
+      <c r="Q3" s="108"/>
+      <c r="R3" s="108"/>
+      <c r="S3" s="108"/>
+      <c r="T3" s="108"/>
+      <c r="U3" s="108"/>
+      <c r="V3" s="108"/>
+      <c r="W3" s="108"/>
+      <c r="X3" s="108"/>
+      <c r="Y3" s="109"/>
     </row>
     <row r="4" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="160"/>
-      <c r="B4" s="161"/>
-      <c r="C4" s="161"/>
-      <c r="D4" s="161"/>
-      <c r="E4" s="161"/>
-      <c r="F4" s="161"/>
-      <c r="G4" s="161"/>
-      <c r="H4" s="161"/>
-      <c r="I4" s="161"/>
-      <c r="J4" s="161"/>
-      <c r="K4" s="161"/>
-      <c r="L4" s="161"/>
-      <c r="M4" s="161"/>
-      <c r="N4" s="161"/>
-      <c r="O4" s="161"/>
-      <c r="P4" s="161"/>
-      <c r="Q4" s="161"/>
-      <c r="R4" s="161"/>
-      <c r="S4" s="161"/>
-      <c r="T4" s="161"/>
-      <c r="U4" s="161"/>
-      <c r="V4" s="161"/>
-      <c r="W4" s="161"/>
-      <c r="X4" s="161"/>
-      <c r="Y4" s="162"/>
+      <c r="A4" s="110"/>
+      <c r="B4" s="111"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="111"/>
+      <c r="M4" s="111"/>
+      <c r="N4" s="111"/>
+      <c r="O4" s="111"/>
+      <c r="P4" s="111"/>
+      <c r="Q4" s="111"/>
+      <c r="R4" s="111"/>
+      <c r="S4" s="111"/>
+      <c r="T4" s="111"/>
+      <c r="U4" s="111"/>
+      <c r="V4" s="111"/>
+      <c r="W4" s="111"/>
+      <c r="X4" s="111"/>
+      <c r="Y4" s="112"/>
     </row>
     <row r="5" spans="1:27" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
@@ -8840,81 +8840,81 @@
       <c r="Y7" s="39"/>
     </row>
     <row r="8" spans="1:27" s="40" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="163" t="s">
+      <c r="A8" s="113" t="s">
         <v>162</v>
       </c>
-      <c r="B8" s="166" t="s">
+      <c r="B8" s="116" t="s">
         <v>170</v>
       </c>
-      <c r="C8" s="166"/>
-      <c r="D8" s="166"/>
-      <c r="E8" s="173" t="s">
+      <c r="C8" s="116"/>
+      <c r="D8" s="116"/>
+      <c r="E8" s="123" t="s">
         <v>171</v>
       </c>
-      <c r="F8" s="173"/>
-      <c r="G8" s="173"/>
-      <c r="H8" s="173"/>
-      <c r="I8" s="173"/>
-      <c r="J8" s="173"/>
-      <c r="K8" s="173"/>
-      <c r="L8" s="173"/>
-      <c r="M8" s="173"/>
-      <c r="N8" s="173"/>
-      <c r="O8" s="173"/>
-      <c r="P8" s="173"/>
-      <c r="Q8" s="173"/>
-      <c r="R8" s="173"/>
-      <c r="S8" s="173"/>
-      <c r="T8" s="173"/>
-      <c r="U8" s="173"/>
-      <c r="V8" s="173"/>
-      <c r="W8" s="173"/>
-      <c r="X8" s="173"/>
-      <c r="Y8" s="174"/>
+      <c r="F8" s="123"/>
+      <c r="G8" s="123"/>
+      <c r="H8" s="123"/>
+      <c r="I8" s="123"/>
+      <c r="J8" s="123"/>
+      <c r="K8" s="123"/>
+      <c r="L8" s="123"/>
+      <c r="M8" s="123"/>
+      <c r="N8" s="123"/>
+      <c r="O8" s="123"/>
+      <c r="P8" s="123"/>
+      <c r="Q8" s="123"/>
+      <c r="R8" s="123"/>
+      <c r="S8" s="123"/>
+      <c r="T8" s="123"/>
+      <c r="U8" s="123"/>
+      <c r="V8" s="123"/>
+      <c r="W8" s="123"/>
+      <c r="X8" s="123"/>
+      <c r="Y8" s="124"/>
     </row>
     <row r="9" spans="1:27" s="40" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="164"/>
-      <c r="B9" s="167"/>
-      <c r="C9" s="167"/>
-      <c r="D9" s="167"/>
-      <c r="E9" s="171" t="s">
+      <c r="A9" s="114"/>
+      <c r="B9" s="117"/>
+      <c r="C9" s="117"/>
+      <c r="D9" s="117"/>
+      <c r="E9" s="121" t="s">
         <v>172</v>
       </c>
-      <c r="F9" s="171"/>
-      <c r="G9" s="171"/>
-      <c r="H9" s="175" t="s">
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="125" t="s">
         <v>173</v>
       </c>
-      <c r="I9" s="175"/>
-      <c r="J9" s="175"/>
-      <c r="K9" s="176" t="s">
+      <c r="I9" s="125"/>
+      <c r="J9" s="125"/>
+      <c r="K9" s="126" t="s">
         <v>191</v>
       </c>
-      <c r="L9" s="176"/>
-      <c r="M9" s="176"/>
-      <c r="N9" s="171" t="s">
+      <c r="L9" s="126"/>
+      <c r="M9" s="126"/>
+      <c r="N9" s="121" t="s">
         <v>174</v>
       </c>
-      <c r="O9" s="171"/>
-      <c r="P9" s="171"/>
-      <c r="Q9" s="175" t="s">
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="125" t="s">
         <v>175</v>
       </c>
-      <c r="R9" s="175"/>
-      <c r="S9" s="175"/>
-      <c r="T9" s="171" t="s">
+      <c r="R9" s="125"/>
+      <c r="S9" s="125"/>
+      <c r="T9" s="121" t="s">
         <v>140</v>
       </c>
-      <c r="U9" s="171"/>
-      <c r="V9" s="171"/>
-      <c r="W9" s="171" t="s">
+      <c r="U9" s="121"/>
+      <c r="V9" s="121"/>
+      <c r="W9" s="121" t="s">
         <v>176</v>
       </c>
-      <c r="X9" s="171"/>
-      <c r="Y9" s="172"/>
+      <c r="X9" s="121"/>
+      <c r="Y9" s="122"/>
     </row>
     <row r="10" spans="1:27" s="40" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="165"/>
+      <c r="A10" s="115"/>
       <c r="B10" s="41" t="s">
         <v>169</v>
       </c>
@@ -11052,14 +11052,14 @@
       <c r="A39" s="96"/>
     </row>
     <row r="40" spans="1:45" s="40" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="177" t="s">
+      <c r="A40" s="127" t="s">
         <v>155</v>
       </c>
-      <c r="B40" s="178"/>
-      <c r="C40" s="178"/>
-      <c r="D40" s="178"/>
-      <c r="E40" s="178"/>
-      <c r="F40" s="178"/>
+      <c r="B40" s="128"/>
+      <c r="C40" s="128"/>
+      <c r="D40" s="128"/>
+      <c r="E40" s="128"/>
+      <c r="F40" s="128"/>
       <c r="G40" s="53"/>
       <c r="H40" s="53"/>
       <c r="I40" s="53"/>
@@ -11081,33 +11081,33 @@
       <c r="Y40" s="54"/>
     </row>
     <row r="41" spans="1:45" s="105" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="168" t="s">
+      <c r="A41" s="118" t="s">
         <v>156</v>
       </c>
-      <c r="B41" s="169"/>
-      <c r="C41" s="169"/>
-      <c r="D41" s="169"/>
-      <c r="E41" s="169"/>
-      <c r="F41" s="169"/>
-      <c r="G41" s="169"/>
-      <c r="H41" s="169"/>
-      <c r="I41" s="169"/>
-      <c r="J41" s="169"/>
-      <c r="K41" s="169"/>
-      <c r="L41" s="169"/>
-      <c r="M41" s="169"/>
-      <c r="N41" s="169"/>
-      <c r="O41" s="169"/>
-      <c r="P41" s="169"/>
-      <c r="Q41" s="169"/>
-      <c r="R41" s="169"/>
-      <c r="S41" s="169"/>
-      <c r="T41" s="169"/>
-      <c r="U41" s="169"/>
-      <c r="V41" s="169"/>
-      <c r="W41" s="169"/>
-      <c r="X41" s="169"/>
-      <c r="Y41" s="170"/>
+      <c r="B41" s="119"/>
+      <c r="C41" s="119"/>
+      <c r="D41" s="119"/>
+      <c r="E41" s="119"/>
+      <c r="F41" s="119"/>
+      <c r="G41" s="119"/>
+      <c r="H41" s="119"/>
+      <c r="I41" s="119"/>
+      <c r="J41" s="119"/>
+      <c r="K41" s="119"/>
+      <c r="L41" s="119"/>
+      <c r="M41" s="119"/>
+      <c r="N41" s="119"/>
+      <c r="O41" s="119"/>
+      <c r="P41" s="119"/>
+      <c r="Q41" s="119"/>
+      <c r="R41" s="119"/>
+      <c r="S41" s="119"/>
+      <c r="T41" s="119"/>
+      <c r="U41" s="119"/>
+      <c r="V41" s="119"/>
+      <c r="W41" s="119"/>
+      <c r="X41" s="119"/>
+      <c r="Y41" s="120"/>
     </row>
     <row r="42" spans="1:45" s="56" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="50" t="s">
